--- a/analyst/Franzi/rmonize/data_proc_elem/DPE_DEGS1_FRANZI.xlsx
+++ b/analyst/Franzi/rmonize/data_proc_elem/DPE_DEGS1_FRANZI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Projekte\NFDI4Health\TA5\Pilotprojekte\Harmonisierung\HarmonizR\use-cases-harmonisation\analyst\Franzi\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{F471681D-9437-4989-90D5-337B2EBE7E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12ECF6FB-D33C-48E1-A501-FDF43EAB843A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="374">
   <si>
     <t>index</t>
   </si>
@@ -1087,13 +1087,88 @@
   </si>
   <si>
     <t>unavailable</t>
+  </si>
+  <si>
+    <t>SEX</t>
+  </si>
+  <si>
+    <t>AGE_BASE</t>
+  </si>
+  <si>
+    <t>EDU_LEVEL</t>
+  </si>
+  <si>
+    <t>TOT_PA_QX</t>
+  </si>
+  <si>
+    <t>SMOKE_ST</t>
+  </si>
+  <si>
+    <t>BMI</t>
+  </si>
+  <si>
+    <t>ENERGY</t>
+  </si>
+  <si>
+    <t>sex</t>
+  </si>
+  <si>
+    <t>Sex</t>
+  </si>
+  <si>
+    <t>Age at exposure measure [years]</t>
+  </si>
+  <si>
+    <t>Highest level of education [ISCED 2011]</t>
+  </si>
+  <si>
+    <t>Physical activity from questionnaire data [MET-hr/day]</t>
+  </si>
+  <si>
+    <t>Smoking status</t>
+  </si>
+  <si>
+    <t>Body Mass Index at baseline [kg/m²]</t>
+  </si>
+  <si>
+    <t>Energy intake [kcal/d]</t>
+  </si>
+  <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t>Rauchstatus in 3 Kategorien</t>
+  </si>
+  <si>
+    <t>SDisced97z</t>
+  </si>
+  <si>
+    <t>Usbmi</t>
+  </si>
+  <si>
+    <t>KAempf_k</t>
+  </si>
+  <si>
+    <t>recode</t>
+  </si>
+  <si>
+    <t>RCstat_k</t>
+  </si>
+  <si>
+    <t>Kategorien siehe DD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1=3;2=2;3=1;ELSE=4) </t>
+  </si>
+  <si>
+    <t>tba</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1142,6 +1217,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1169,7 +1251,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1203,6 +1285,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1507,7 +1590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L121"/>
+  <dimension ref="A1:L128"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
@@ -1557,44 +1640,42 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>11</v>
+        <v>349</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>357</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>260</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>265</v>
+        <v>356</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>273</v>
       </c>
       <c r="H2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>347</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="I2" s="3"/>
       <c r="J2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>18</v>
+        <v>350</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>358</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
@@ -1603,59 +1684,60 @@
         <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>265</v>
+        <v>364</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>273</v>
       </c>
       <c r="H3" t="s">
-        <v>266</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>267</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="I3" s="3"/>
       <c r="J3" t="s">
         <v>20</v>
       </c>
       <c r="K3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>351</v>
+      </c>
+      <c r="C4" t="s">
+        <v>359</v>
+      </c>
+      <c r="D4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>366</v>
+      </c>
+      <c r="G4" t="s">
+        <v>369</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>373</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="J4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>25</v>
+        <v>352</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>360</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
@@ -1664,175 +1746,184 @@
         <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>268</v>
+        <v>368</v>
       </c>
       <c r="G5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C6" t="s">
+        <v>361</v>
+      </c>
+      <c r="D6" t="s">
+        <v>260</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>370</v>
+      </c>
+      <c r="G6" t="s">
+        <v>369</v>
+      </c>
+      <c r="H6" t="s">
+        <v>372</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="J6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>354</v>
+      </c>
+      <c r="C7" t="s">
+        <v>362</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" t="s">
+        <v>367</v>
+      </c>
+      <c r="G7" t="s">
+        <v>273</v>
+      </c>
+      <c r="H7" t="s">
+        <v>273</v>
+      </c>
+      <c r="I7" s="3"/>
+      <c r="J7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>355</v>
+      </c>
+      <c r="C8" t="s">
+        <v>363</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="3"/>
+      <c r="J8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s">
+        <v>265</v>
+      </c>
+      <c r="G9" t="s">
         <v>15</v>
       </c>
-      <c r="H5" t="s">
-        <v>269</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="H9" t="s">
+        <v>266</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="J9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" t="s">
+        <v>265</v>
+      </c>
+      <c r="G10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" t="s">
+        <v>266</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="J10" t="s">
         <v>20</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K10" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K6" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K7" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" t="s">
-        <v>24</v>
-      </c>
-      <c r="K8" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" t="s">
-        <v>24</v>
-      </c>
-      <c r="K9" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J10" t="s">
-        <v>24</v>
-      </c>
-      <c r="K10" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
@@ -1856,12 +1947,12 @@
         <v>348</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D12" t="s">
         <v>13</v>
@@ -1870,27 +1961,30 @@
         <v>14</v>
       </c>
       <c r="F12" t="s">
-        <v>24</v>
+        <v>268</v>
       </c>
       <c r="G12" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>24</v>
+        <v>269</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>270</v>
       </c>
       <c r="J12" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K12" t="s">
-        <v>348</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D13" t="s">
         <v>13</v>
@@ -1916,10 +2010,10 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D14" t="s">
         <v>13</v>
@@ -1945,10 +2039,10 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s">
         <v>13</v>
@@ -1957,30 +2051,27 @@
         <v>14</v>
       </c>
       <c r="F15" t="s">
-        <v>271</v>
+        <v>24</v>
       </c>
       <c r="G15" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="H15" t="s">
-        <v>273</v>
-      </c>
-      <c r="I15" t="s">
-        <v>272</v>
+        <v>24</v>
       </c>
       <c r="J15" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K15" t="s">
-        <v>263</v>
+        <v>348</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s">
         <v>13</v>
@@ -2004,12 +2095,12 @@
         <v>348</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s">
         <v>13</v>
@@ -2018,30 +2109,27 @@
         <v>14</v>
       </c>
       <c r="F17" t="s">
-        <v>275</v>
+        <v>24</v>
       </c>
       <c r="G17" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H17" t="s">
-        <v>276</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>277</v>
+        <v>24</v>
       </c>
       <c r="J17" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K17" t="s">
-        <v>21</v>
+        <v>348</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s">
         <v>13</v>
@@ -2050,28 +2138,27 @@
         <v>14</v>
       </c>
       <c r="F18" t="s">
-        <v>278</v>
+        <v>24</v>
       </c>
       <c r="G18" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="H18" t="s">
-        <v>273</v>
-      </c>
-      <c r="I18" s="9"/>
+        <v>24</v>
+      </c>
       <c r="J18" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K18" t="s">
-        <v>263</v>
+        <v>348</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="D19" t="s">
         <v>13</v>
@@ -2080,27 +2167,27 @@
         <v>14</v>
       </c>
       <c r="F19" t="s">
-        <v>279</v>
+        <v>24</v>
       </c>
       <c r="G19" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="H19" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="J19" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K19" t="s">
-        <v>263</v>
+        <v>348</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="D20" t="s">
         <v>13</v>
@@ -2109,27 +2196,27 @@
         <v>14</v>
       </c>
       <c r="F20" t="s">
-        <v>274</v>
+        <v>24</v>
       </c>
       <c r="G20" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="H20" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="J20" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K20" t="s">
-        <v>263</v>
+        <v>348</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="D21" t="s">
         <v>13</v>
@@ -2155,10 +2242,10 @@
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="D22" t="s">
         <v>13</v>
@@ -2166,31 +2253,31 @@
       <c r="E22" t="s">
         <v>14</v>
       </c>
-      <c r="F22" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>339</v>
+      <c r="F22" t="s">
+        <v>271</v>
+      </c>
+      <c r="G22" t="s">
+        <v>273</v>
+      </c>
+      <c r="H22" t="s">
+        <v>273</v>
       </c>
       <c r="I22" t="s">
-        <v>340</v>
+        <v>272</v>
       </c>
       <c r="J22" t="s">
         <v>20</v>
       </c>
       <c r="K22" t="s">
-        <v>21</v>
+        <v>263</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="C23" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="D23" t="s">
         <v>13</v>
@@ -2199,122 +2286,118 @@
         <v>14</v>
       </c>
       <c r="F23" t="s">
-        <v>280</v>
+        <v>24</v>
       </c>
       <c r="G23" t="s">
+        <v>24</v>
+      </c>
+      <c r="H23" t="s">
+        <v>24</v>
+      </c>
+      <c r="J23" t="s">
+        <v>24</v>
+      </c>
+      <c r="K23" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" t="s">
+        <v>275</v>
+      </c>
+      <c r="G24" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" t="s">
+        <v>276</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="J24" t="s">
+        <v>20</v>
+      </c>
+      <c r="K24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" t="s">
+        <v>278</v>
+      </c>
+      <c r="G25" t="s">
         <v>273</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H25" t="s">
         <v>273</v>
       </c>
-      <c r="J23" t="s">
+      <c r="I25" s="9"/>
+      <c r="J25" t="s">
         <v>20</v>
       </c>
-      <c r="K23" t="s">
+      <c r="K25" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24" t="s">
-        <v>64</v>
-      </c>
-      <c r="D24" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" t="s">
-        <v>24</v>
-      </c>
-      <c r="G24" t="s">
-        <v>24</v>
-      </c>
-      <c r="H24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J24" t="s">
-        <v>24</v>
-      </c>
-      <c r="K24" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
-        <v>65</v>
-      </c>
-      <c r="C25" t="s">
-        <v>66</v>
-      </c>
-      <c r="D25" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>281</v>
-      </c>
-      <c r="G25" s="10" t="s">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" t="s">
+        <v>279</v>
+      </c>
+      <c r="G26" t="s">
         <v>273</v>
       </c>
-      <c r="H25" s="10" t="s">
+      <c r="H26" t="s">
         <v>273</v>
       </c>
-      <c r="I25" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="J25" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="K25" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="L25" s="10"/>
-    </row>
-    <row r="26" spans="2:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" t="s">
-        <v>68</v>
-      </c>
-      <c r="D26" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" t="s">
-        <v>14</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="H26" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="I26" s="16" t="s">
-        <v>346</v>
-      </c>
-      <c r="J26" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="K26" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="L26" s="10"/>
+      <c r="J26" t="s">
+        <v>20</v>
+      </c>
+      <c r="K26" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="C27" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="D27" t="s">
         <v>13</v>
@@ -2322,30 +2405,28 @@
       <c r="E27" t="s">
         <v>14</v>
       </c>
-      <c r="F27" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="G27" s="10" t="s">
+      <c r="F27" t="s">
+        <v>274</v>
+      </c>
+      <c r="G27" t="s">
         <v>273</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="H27" t="s">
         <v>273</v>
       </c>
-      <c r="I27" s="11"/>
-      <c r="J27" s="10" t="s">
+      <c r="J27" t="s">
         <v>20</v>
       </c>
-      <c r="K27" s="10" t="s">
+      <c r="K27" t="s">
         <v>263</v>
       </c>
-      <c r="L27" s="10"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="C28" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="D28" t="s">
         <v>13</v>
@@ -2371,10 +2452,10 @@
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="C29" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="D29" t="s">
         <v>13</v>
@@ -2382,28 +2463,31 @@
       <c r="E29" t="s">
         <v>14</v>
       </c>
-      <c r="F29" t="s">
-        <v>24</v>
-      </c>
-      <c r="G29" t="s">
-        <v>24</v>
-      </c>
-      <c r="H29" t="s">
-        <v>24</v>
+      <c r="F29" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="I29" t="s">
+        <v>340</v>
       </c>
       <c r="J29" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K29" t="s">
-        <v>348</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C30" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="D30" t="s">
         <v>13</v>
@@ -2412,370 +2496,374 @@
         <v>14</v>
       </c>
       <c r="F30" t="s">
-        <v>24</v>
+        <v>280</v>
       </c>
       <c r="G30" t="s">
-        <v>24</v>
+        <v>273</v>
       </c>
       <c r="H30" t="s">
-        <v>24</v>
+        <v>273</v>
       </c>
       <c r="J30" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K30" t="s">
-        <v>348</v>
+        <v>263</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" t="s">
+        <v>64</v>
+      </c>
+      <c r="D31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" t="s">
+        <v>14</v>
+      </c>
+      <c r="F31" t="s">
+        <v>24</v>
+      </c>
+      <c r="G31" t="s">
+        <v>24</v>
+      </c>
+      <c r="H31" t="s">
+        <v>24</v>
+      </c>
+      <c r="J31" t="s">
+        <v>24</v>
+      </c>
+      <c r="K31" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" t="s">
+        <v>14</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="K32" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L32" s="10"/>
+    </row>
+    <row r="33" spans="2:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="I33" s="16" t="s">
+        <v>346</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="K33" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L33" s="10"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" t="s">
+        <v>70</v>
+      </c>
+      <c r="D34" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" t="s">
+        <v>14</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="I34" s="11"/>
+      <c r="J34" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K34" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="L34" s="10"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35" t="s">
+        <v>24</v>
+      </c>
+      <c r="G35" t="s">
+        <v>24</v>
+      </c>
+      <c r="H35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J35" t="s">
+        <v>24</v>
+      </c>
+      <c r="K35" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" t="s">
+        <v>74</v>
+      </c>
+      <c r="D36" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" t="s">
+        <v>14</v>
+      </c>
+      <c r="F36" t="s">
+        <v>24</v>
+      </c>
+      <c r="G36" t="s">
+        <v>24</v>
+      </c>
+      <c r="H36" t="s">
+        <v>24</v>
+      </c>
+      <c r="J36" t="s">
+        <v>24</v>
+      </c>
+      <c r="K36" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>75</v>
+      </c>
+      <c r="C37" t="s">
+        <v>76</v>
+      </c>
+      <c r="D37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F37" t="s">
+        <v>24</v>
+      </c>
+      <c r="G37" t="s">
+        <v>24</v>
+      </c>
+      <c r="H37" t="s">
+        <v>24</v>
+      </c>
+      <c r="J37" t="s">
+        <v>24</v>
+      </c>
+      <c r="K37" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
         <v>77</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C38" t="s">
         <v>78</v>
       </c>
-      <c r="D31" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31" t="s">
-        <v>14</v>
-      </c>
-      <c r="F31" t="s">
-        <v>24</v>
-      </c>
-      <c r="G31" t="s">
-        <v>24</v>
-      </c>
-      <c r="H31" t="s">
-        <v>24</v>
-      </c>
-      <c r="J31" t="s">
-        <v>24</v>
-      </c>
-      <c r="K31" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
+      <c r="D38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" t="s">
+        <v>14</v>
+      </c>
+      <c r="F38" t="s">
+        <v>24</v>
+      </c>
+      <c r="G38" t="s">
+        <v>24</v>
+      </c>
+      <c r="H38" t="s">
+        <v>24</v>
+      </c>
+      <c r="J38" t="s">
+        <v>24</v>
+      </c>
+      <c r="K38" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
         <v>79</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C39" t="s">
         <v>80</v>
       </c>
-      <c r="D32" t="s">
-        <v>13</v>
-      </c>
-      <c r="E32" t="s">
-        <v>14</v>
-      </c>
-      <c r="F32" t="s">
-        <v>24</v>
-      </c>
-      <c r="G32" t="s">
-        <v>24</v>
-      </c>
-      <c r="H32" t="s">
-        <v>24</v>
-      </c>
-      <c r="J32" t="s">
-        <v>24</v>
-      </c>
-      <c r="K32" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B33" t="s">
+      <c r="D39" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" t="s">
+        <v>14</v>
+      </c>
+      <c r="F39" t="s">
+        <v>24</v>
+      </c>
+      <c r="G39" t="s">
+        <v>24</v>
+      </c>
+      <c r="H39" t="s">
+        <v>24</v>
+      </c>
+      <c r="J39" t="s">
+        <v>24</v>
+      </c>
+      <c r="K39" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
         <v>81</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C40" t="s">
         <v>82</v>
       </c>
-      <c r="D33" t="s">
-        <v>13</v>
-      </c>
-      <c r="E33" t="s">
-        <v>14</v>
-      </c>
-      <c r="F33" t="s">
-        <v>24</v>
-      </c>
-      <c r="G33" t="s">
-        <v>24</v>
-      </c>
-      <c r="H33" t="s">
-        <v>24</v>
-      </c>
-      <c r="J33" t="s">
-        <v>24</v>
-      </c>
-      <c r="K33" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B34" t="s">
+      <c r="D40" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" t="s">
+        <v>14</v>
+      </c>
+      <c r="F40" t="s">
+        <v>24</v>
+      </c>
+      <c r="G40" t="s">
+        <v>24</v>
+      </c>
+      <c r="H40" t="s">
+        <v>24</v>
+      </c>
+      <c r="J40" t="s">
+        <v>24</v>
+      </c>
+      <c r="K40" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
         <v>83</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C41" t="s">
         <v>84</v>
       </c>
-      <c r="D34" t="s">
-        <v>13</v>
-      </c>
-      <c r="E34" t="s">
-        <v>14</v>
-      </c>
-      <c r="F34" t="s">
-        <v>24</v>
-      </c>
-      <c r="G34" t="s">
-        <v>24</v>
-      </c>
-      <c r="H34" t="s">
-        <v>24</v>
-      </c>
-      <c r="J34" t="s">
-        <v>24</v>
-      </c>
-      <c r="K34" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B35" t="s">
+      <c r="D41" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" t="s">
+        <v>14</v>
+      </c>
+      <c r="F41" t="s">
+        <v>24</v>
+      </c>
+      <c r="G41" t="s">
+        <v>24</v>
+      </c>
+      <c r="H41" t="s">
+        <v>24</v>
+      </c>
+      <c r="J41" t="s">
+        <v>24</v>
+      </c>
+      <c r="K41" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
         <v>85</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C42" t="s">
         <v>86</v>
       </c>
-      <c r="D35" t="s">
-        <v>13</v>
-      </c>
-      <c r="E35" t="s">
-        <v>14</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="D42" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" t="s">
+        <v>14</v>
+      </c>
+      <c r="F42" t="s">
         <v>285</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G42" t="s">
         <v>15</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H42" t="s">
         <v>284</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I42" t="s">
         <v>286</v>
-      </c>
-      <c r="J35" t="s">
-        <v>20</v>
-      </c>
-      <c r="K35" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B36" t="s">
-        <v>87</v>
-      </c>
-      <c r="C36" t="s">
-        <v>88</v>
-      </c>
-      <c r="D36" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" t="s">
-        <v>14</v>
-      </c>
-      <c r="F36" t="s">
-        <v>287</v>
-      </c>
-      <c r="G36" t="s">
-        <v>15</v>
-      </c>
-      <c r="H36" t="s">
-        <v>288</v>
-      </c>
-      <c r="I36" t="s">
-        <v>289</v>
-      </c>
-      <c r="J36" t="s">
-        <v>20</v>
-      </c>
-      <c r="K36" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B37" t="s">
-        <v>89</v>
-      </c>
-      <c r="C37" t="s">
-        <v>90</v>
-      </c>
-      <c r="D37" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" t="s">
-        <v>14</v>
-      </c>
-      <c r="F37" t="s">
-        <v>24</v>
-      </c>
-      <c r="G37" t="s">
-        <v>24</v>
-      </c>
-      <c r="H37" t="s">
-        <v>24</v>
-      </c>
-      <c r="J37" t="s">
-        <v>24</v>
-      </c>
-      <c r="K37" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B38" t="s">
-        <v>91</v>
-      </c>
-      <c r="C38" t="s">
-        <v>92</v>
-      </c>
-      <c r="D38" t="s">
-        <v>13</v>
-      </c>
-      <c r="E38" t="s">
-        <v>14</v>
-      </c>
-      <c r="F38" t="s">
-        <v>24</v>
-      </c>
-      <c r="G38" t="s">
-        <v>24</v>
-      </c>
-      <c r="H38" t="s">
-        <v>24</v>
-      </c>
-      <c r="J38" t="s">
-        <v>24</v>
-      </c>
-      <c r="K38" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B39" t="s">
-        <v>93</v>
-      </c>
-      <c r="C39" t="s">
-        <v>94</v>
-      </c>
-      <c r="D39" t="s">
-        <v>13</v>
-      </c>
-      <c r="E39" t="s">
-        <v>14</v>
-      </c>
-      <c r="F39" t="s">
-        <v>290</v>
-      </c>
-      <c r="G39" t="s">
-        <v>15</v>
-      </c>
-      <c r="H39" t="s">
-        <v>291</v>
-      </c>
-      <c r="I39" t="s">
-        <v>292</v>
-      </c>
-      <c r="J39" t="s">
-        <v>20</v>
-      </c>
-      <c r="K39" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B40" t="s">
-        <v>95</v>
-      </c>
-      <c r="C40" t="s">
-        <v>96</v>
-      </c>
-      <c r="D40" t="s">
-        <v>13</v>
-      </c>
-      <c r="E40" t="s">
-        <v>14</v>
-      </c>
-      <c r="F40" t="s">
-        <v>293</v>
-      </c>
-      <c r="G40" t="s">
-        <v>273</v>
-      </c>
-      <c r="H40" t="s">
-        <v>273</v>
-      </c>
-      <c r="J40" t="s">
-        <v>20</v>
-      </c>
-      <c r="K40" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B41" t="s">
-        <v>97</v>
-      </c>
-      <c r="C41" t="s">
-        <v>98</v>
-      </c>
-      <c r="D41" t="s">
-        <v>13</v>
-      </c>
-      <c r="E41" t="s">
-        <v>14</v>
-      </c>
-      <c r="F41" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="G41" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J41" t="s">
-        <v>24</v>
-      </c>
-      <c r="K41" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B42" t="s">
-        <v>99</v>
-      </c>
-      <c r="C42" t="s">
-        <v>100</v>
-      </c>
-      <c r="D42" t="s">
-        <v>13</v>
-      </c>
-      <c r="E42" t="s">
-        <v>14</v>
-      </c>
-      <c r="F42" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="G42" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H42" s="10" t="s">
-        <v>342</v>
       </c>
       <c r="J42" t="s">
         <v>20</v>
@@ -2784,12 +2872,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C43" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D43" t="s">
         <v>13</v>
@@ -2797,145 +2885,150 @@
       <c r="E43" t="s">
         <v>14</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="G43" s="10" t="s">
+      <c r="F43" t="s">
+        <v>287</v>
+      </c>
+      <c r="G43" t="s">
+        <v>15</v>
+      </c>
+      <c r="H43" t="s">
+        <v>288</v>
+      </c>
+      <c r="I43" t="s">
+        <v>289</v>
+      </c>
+      <c r="J43" t="s">
+        <v>20</v>
+      </c>
+      <c r="K43" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>89</v>
+      </c>
+      <c r="C44" t="s">
+        <v>90</v>
+      </c>
+      <c r="D44" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" t="s">
+        <v>14</v>
+      </c>
+      <c r="F44" t="s">
+        <v>24</v>
+      </c>
+      <c r="G44" t="s">
+        <v>24</v>
+      </c>
+      <c r="H44" t="s">
+        <v>24</v>
+      </c>
+      <c r="J44" t="s">
+        <v>24</v>
+      </c>
+      <c r="K44" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>91</v>
+      </c>
+      <c r="C45" t="s">
+        <v>92</v>
+      </c>
+      <c r="D45" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" t="s">
+        <v>14</v>
+      </c>
+      <c r="F45" t="s">
+        <v>24</v>
+      </c>
+      <c r="G45" t="s">
+        <v>24</v>
+      </c>
+      <c r="H45" t="s">
+        <v>24</v>
+      </c>
+      <c r="J45" t="s">
+        <v>24</v>
+      </c>
+      <c r="K45" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>93</v>
+      </c>
+      <c r="C46" t="s">
+        <v>94</v>
+      </c>
+      <c r="D46" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" t="s">
+        <v>14</v>
+      </c>
+      <c r="F46" t="s">
+        <v>290</v>
+      </c>
+      <c r="G46" t="s">
+        <v>15</v>
+      </c>
+      <c r="H46" t="s">
+        <v>291</v>
+      </c>
+      <c r="I46" t="s">
+        <v>292</v>
+      </c>
+      <c r="J46" t="s">
+        <v>20</v>
+      </c>
+      <c r="K46" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>95</v>
+      </c>
+      <c r="C47" t="s">
+        <v>96</v>
+      </c>
+      <c r="D47" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" t="s">
+        <v>14</v>
+      </c>
+      <c r="F47" t="s">
+        <v>293</v>
+      </c>
+      <c r="G47" t="s">
         <v>273</v>
       </c>
-      <c r="H43" s="10" t="s">
+      <c r="H47" t="s">
         <v>273</v>
       </c>
-      <c r="I43" s="11"/>
-      <c r="J43" s="10" t="s">
+      <c r="J47" t="s">
         <v>20</v>
       </c>
-      <c r="K43" s="10" t="s">
+      <c r="K47" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B44" t="s">
-        <v>103</v>
-      </c>
-      <c r="C44" t="s">
-        <v>104</v>
-      </c>
-      <c r="D44" t="s">
-        <v>13</v>
-      </c>
-      <c r="E44" t="s">
-        <v>14</v>
-      </c>
-      <c r="F44" t="s">
-        <v>24</v>
-      </c>
-      <c r="G44" t="s">
-        <v>24</v>
-      </c>
-      <c r="H44" t="s">
-        <v>24</v>
-      </c>
-      <c r="J44" t="s">
-        <v>24</v>
-      </c>
-      <c r="K44" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B45" t="s">
-        <v>105</v>
-      </c>
-      <c r="C45" t="s">
-        <v>106</v>
-      </c>
-      <c r="D45" t="s">
-        <v>13</v>
-      </c>
-      <c r="E45" t="s">
-        <v>14</v>
-      </c>
-      <c r="F45" t="s">
-        <v>24</v>
-      </c>
-      <c r="G45" t="s">
-        <v>24</v>
-      </c>
-      <c r="H45" t="s">
-        <v>24</v>
-      </c>
-      <c r="J45" t="s">
-        <v>24</v>
-      </c>
-      <c r="K45" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B46" t="s">
-        <v>107</v>
-      </c>
-      <c r="C46" t="s">
-        <v>108</v>
-      </c>
-      <c r="D46" t="s">
-        <v>13</v>
-      </c>
-      <c r="E46" t="s">
-        <v>14</v>
-      </c>
-      <c r="F46" t="s">
-        <v>24</v>
-      </c>
-      <c r="G46" t="s">
-        <v>24</v>
-      </c>
-      <c r="H46" t="s">
-        <v>24</v>
-      </c>
-      <c r="J46" t="s">
-        <v>24</v>
-      </c>
-      <c r="K46" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B47" t="s">
-        <v>109</v>
-      </c>
-      <c r="C47" t="s">
-        <v>110</v>
-      </c>
-      <c r="D47" t="s">
-        <v>13</v>
-      </c>
-      <c r="E47" t="s">
-        <v>14</v>
-      </c>
-      <c r="F47" t="s">
-        <v>24</v>
-      </c>
-      <c r="G47" t="s">
-        <v>24</v>
-      </c>
-      <c r="H47" t="s">
-        <v>24</v>
-      </c>
-      <c r="J47" t="s">
-        <v>24</v>
-      </c>
-      <c r="K47" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C48" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="D48" t="s">
         <v>13</v>
@@ -2943,13 +3036,13 @@
       <c r="E48" t="s">
         <v>14</v>
       </c>
-      <c r="F48" t="s">
-        <v>24</v>
-      </c>
-      <c r="G48" t="s">
-        <v>24</v>
-      </c>
-      <c r="H48" t="s">
+      <c r="F48" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H48" s="10" t="s">
         <v>24</v>
       </c>
       <c r="J48" t="s">
@@ -2961,10 +3054,10 @@
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="C49" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="D49" t="s">
         <v>13</v>
@@ -2972,28 +3065,28 @@
       <c r="E49" t="s">
         <v>14</v>
       </c>
-      <c r="F49" t="s">
-        <v>24</v>
-      </c>
-      <c r="G49" t="s">
-        <v>24</v>
-      </c>
-      <c r="H49" t="s">
-        <v>24</v>
+      <c r="F49" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="G49" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>342</v>
       </c>
       <c r="J49" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K49" t="s">
-        <v>348</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="C50" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="D50" t="s">
         <v>13</v>
@@ -3002,7 +3095,7 @@
         <v>14</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G50" s="10" t="s">
         <v>273</v>
@@ -3017,14 +3110,13 @@
       <c r="K50" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="L50" s="10"/>
     </row>
     <row r="51" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="C51" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="D51" t="s">
         <v>13</v>
@@ -3050,10 +3142,10 @@
     </row>
     <row r="52" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C52" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="D52" t="s">
         <v>13</v>
@@ -3079,10 +3171,10 @@
     </row>
     <row r="53" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="C53" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D53" t="s">
         <v>13</v>
@@ -3108,10 +3200,10 @@
     </row>
     <row r="54" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="C54" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="D54" t="s">
         <v>13</v>
@@ -3137,10 +3229,10 @@
     </row>
     <row r="55" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="C55" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D55" t="s">
         <v>13</v>
@@ -3166,10 +3258,10 @@
     </row>
     <row r="56" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="C56" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D56" t="s">
         <v>13</v>
@@ -3195,10 +3287,10 @@
     </row>
     <row r="57" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C57" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="D57" t="s">
         <v>13</v>
@@ -3206,28 +3298,30 @@
       <c r="E57" t="s">
         <v>14</v>
       </c>
-      <c r="F57" t="s">
-        <v>24</v>
-      </c>
-      <c r="G57" t="s">
-        <v>24</v>
-      </c>
-      <c r="H57" t="s">
-        <v>24</v>
-      </c>
-      <c r="J57" t="s">
-        <v>24</v>
-      </c>
-      <c r="K57" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="58" spans="2:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="F57" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="I57" s="11"/>
+      <c r="J57" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K57" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="L57" s="10"/>
+    </row>
+    <row r="58" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="C58" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="D58" t="s">
         <v>13</v>
@@ -3235,31 +3329,28 @@
       <c r="E58" t="s">
         <v>14</v>
       </c>
-      <c r="F58" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="G58" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H58" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="I58" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="J58" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="K58" s="10" t="s">
-        <v>21</v>
+      <c r="F58" t="s">
+        <v>24</v>
+      </c>
+      <c r="G58" t="s">
+        <v>24</v>
+      </c>
+      <c r="H58" t="s">
+        <v>24</v>
+      </c>
+      <c r="J58" t="s">
+        <v>24</v>
+      </c>
+      <c r="K58" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="59" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="C59" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="D59" t="s">
         <v>13</v>
@@ -3285,10 +3376,10 @@
     </row>
     <row r="60" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="C60" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="D60" t="s">
         <v>13</v>
@@ -3312,12 +3403,12 @@
         <v>348</v>
       </c>
     </row>
-    <row r="61" spans="2:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="C61" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="D61" t="s">
         <v>13</v>
@@ -3325,31 +3416,28 @@
       <c r="E61" t="s">
         <v>14</v>
       </c>
-      <c r="F61" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="G61" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="I61" s="12" t="s">
-        <v>301</v>
-      </c>
-      <c r="J61" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="K61" s="10" t="s">
-        <v>21</v>
+      <c r="F61" t="s">
+        <v>24</v>
+      </c>
+      <c r="G61" t="s">
+        <v>24</v>
+      </c>
+      <c r="H61" t="s">
+        <v>24</v>
+      </c>
+      <c r="J61" t="s">
+        <v>24</v>
+      </c>
+      <c r="K61" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="62" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="C62" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="D62" t="s">
         <v>13</v>
@@ -3375,10 +3463,10 @@
     </row>
     <row r="63" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="C63" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="D63" t="s">
         <v>13</v>
@@ -3404,10 +3492,10 @@
     </row>
     <row r="64" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="C64" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="D64" t="s">
         <v>13</v>
@@ -3416,27 +3504,27 @@
         <v>14</v>
       </c>
       <c r="F64" t="s">
-        <v>302</v>
+        <v>24</v>
       </c>
       <c r="G64" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="H64" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="J64" t="s">
-        <v>145</v>
+        <v>24</v>
       </c>
       <c r="K64" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="C65" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="D65" t="s">
         <v>13</v>
@@ -3444,61 +3532,60 @@
       <c r="E65" t="s">
         <v>14</v>
       </c>
-      <c r="F65" t="s">
-        <v>24</v>
-      </c>
-      <c r="G65" t="s">
-        <v>24</v>
-      </c>
-      <c r="H65" t="s">
-        <v>24</v>
-      </c>
-      <c r="J65" t="s">
-        <v>24</v>
-      </c>
-      <c r="K65" t="s">
-        <v>348</v>
+      <c r="F65" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="G65" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="I65" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="J65" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K65" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A66" s="13"/>
-      <c r="B66" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="C66" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="D66" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E66" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F66" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="G66" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="H66" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="I66" s="15" t="s">
-        <v>344</v>
-      </c>
-      <c r="J66" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="K66" s="10" t="s">
-        <v>17</v>
+      <c r="B66" t="s">
+        <v>133</v>
+      </c>
+      <c r="C66" t="s">
+        <v>134</v>
+      </c>
+      <c r="D66" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" t="s">
+        <v>14</v>
+      </c>
+      <c r="F66" t="s">
+        <v>24</v>
+      </c>
+      <c r="G66" t="s">
+        <v>24</v>
+      </c>
+      <c r="H66" t="s">
+        <v>24</v>
+      </c>
+      <c r="J66" t="s">
+        <v>24</v>
+      </c>
+      <c r="K66" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="C67" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="D67" t="s">
         <v>13</v>
@@ -3522,12 +3609,12 @@
         <v>348</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="C68" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="D68" t="s">
         <v>13</v>
@@ -3535,28 +3622,31 @@
       <c r="E68" t="s">
         <v>14</v>
       </c>
-      <c r="F68" t="s">
-        <v>24</v>
-      </c>
-      <c r="G68" t="s">
-        <v>24</v>
-      </c>
-      <c r="H68" t="s">
-        <v>24</v>
-      </c>
-      <c r="J68" t="s">
-        <v>24</v>
-      </c>
-      <c r="K68" t="s">
-        <v>348</v>
+      <c r="F68" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="G68" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H68" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="I68" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="J68" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K68" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="C69" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="D69" t="s">
         <v>13</v>
@@ -3582,10 +3672,10 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="C70" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="D70" t="s">
         <v>13</v>
@@ -3611,10 +3701,10 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="C71" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="D71" t="s">
         <v>13</v>
@@ -3623,27 +3713,27 @@
         <v>14</v>
       </c>
       <c r="F71" t="s">
-        <v>24</v>
+        <v>302</v>
       </c>
       <c r="G71" t="s">
-        <v>24</v>
+        <v>273</v>
       </c>
       <c r="H71" t="s">
-        <v>24</v>
+        <v>273</v>
       </c>
       <c r="J71" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="K71" t="s">
-        <v>348</v>
+        <v>263</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="C72" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D72" t="s">
         <v>13</v>
@@ -3668,40 +3758,44 @@
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B73" t="s">
-        <v>162</v>
-      </c>
-      <c r="C73" t="s">
-        <v>163</v>
-      </c>
-      <c r="D73" t="s">
-        <v>13</v>
-      </c>
-      <c r="E73" t="s">
-        <v>14</v>
-      </c>
-      <c r="F73" t="s">
-        <v>24</v>
-      </c>
-      <c r="G73" t="s">
-        <v>24</v>
-      </c>
-      <c r="H73" t="s">
-        <v>24</v>
-      </c>
-      <c r="J73" t="s">
-        <v>24</v>
-      </c>
-      <c r="K73" t="s">
-        <v>348</v>
+      <c r="A73" s="13"/>
+      <c r="B73" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="G73" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="H73" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="I73" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="J73" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="K73" s="10" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="C74" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="D74" t="s">
         <v>13</v>
@@ -3710,30 +3804,27 @@
         <v>14</v>
       </c>
       <c r="F74" t="s">
-        <v>304</v>
+        <v>24</v>
       </c>
       <c r="G74" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H74" t="s">
-        <v>305</v>
-      </c>
-      <c r="I74" t="s">
-        <v>313</v>
+        <v>24</v>
       </c>
       <c r="J74" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K74" t="s">
-        <v>21</v>
+        <v>348</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C75" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="D75" t="s">
         <v>13</v>
@@ -3742,27 +3833,27 @@
         <v>14</v>
       </c>
       <c r="F75" t="s">
-        <v>306</v>
+        <v>24</v>
       </c>
       <c r="G75" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="H75" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="J75" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K75" t="s">
-        <v>263</v>
+        <v>348</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="C76" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="D76" t="s">
         <v>13</v>
@@ -3771,27 +3862,27 @@
         <v>14</v>
       </c>
       <c r="F76" t="s">
-        <v>307</v>
+        <v>24</v>
       </c>
       <c r="G76" t="s">
-        <v>273</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>273</v>
+        <v>24</v>
+      </c>
+      <c r="H76" t="s">
+        <v>24</v>
       </c>
       <c r="J76" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K76" t="s">
-        <v>263</v>
+        <v>348</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="C77" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="D77" t="s">
         <v>13</v>
@@ -3817,10 +3908,10 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="C78" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="D78" t="s">
         <v>13</v>
@@ -3829,27 +3920,27 @@
         <v>14</v>
       </c>
       <c r="F78" t="s">
-        <v>308</v>
+        <v>24</v>
       </c>
       <c r="G78" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="H78" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="J78" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K78" t="s">
-        <v>263</v>
+        <v>348</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="C79" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="D79" t="s">
         <v>13</v>
@@ -3875,10 +3966,10 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="C80" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="D80" t="s">
         <v>13</v>
@@ -3902,12 +3993,12 @@
         <v>348</v>
       </c>
     </row>
-    <row r="81" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="C81" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="D81" t="s">
         <v>13</v>
@@ -3916,27 +4007,30 @@
         <v>14</v>
       </c>
       <c r="F81" t="s">
-        <v>24</v>
+        <v>304</v>
       </c>
       <c r="G81" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H81" t="s">
-        <v>24</v>
+        <v>305</v>
+      </c>
+      <c r="I81" t="s">
+        <v>313</v>
       </c>
       <c r="J81" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K81" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="82" spans="2:12" ht="45" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="C82" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="D82" t="s">
         <v>13</v>
@@ -3945,30 +4039,27 @@
         <v>14</v>
       </c>
       <c r="F82" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="G82" t="s">
-        <v>15</v>
+        <v>273</v>
       </c>
       <c r="H82" t="s">
-        <v>310</v>
-      </c>
-      <c r="I82" s="3" t="s">
-        <v>314</v>
+        <v>273</v>
       </c>
       <c r="J82" t="s">
         <v>20</v>
       </c>
       <c r="K82" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="83" spans="2:12" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="C83" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="D83" t="s">
         <v>13</v>
@@ -3977,27 +4068,27 @@
         <v>14</v>
       </c>
       <c r="F83" t="s">
-        <v>24</v>
+        <v>307</v>
       </c>
       <c r="G83" t="s">
-        <v>24</v>
-      </c>
-      <c r="H83" t="s">
-        <v>24</v>
+        <v>273</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="J83" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K83" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="84" spans="2:12" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="84" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="C84" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="D84" t="s">
         <v>13</v>
@@ -4021,12 +4112,12 @@
         <v>348</v>
       </c>
     </row>
-    <row r="85" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="C85" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="D85" t="s">
         <v>13</v>
@@ -4035,291 +4126,286 @@
         <v>14</v>
       </c>
       <c r="F85" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G85" t="s">
-        <v>15</v>
+        <v>273</v>
       </c>
       <c r="H85" t="s">
-        <v>312</v>
-      </c>
-      <c r="I85" t="s">
-        <v>315</v>
+        <v>273</v>
       </c>
       <c r="J85" t="s">
         <v>20</v>
       </c>
       <c r="K85" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B86" t="s">
+        <v>174</v>
+      </c>
+      <c r="C86" t="s">
+        <v>175</v>
+      </c>
+      <c r="D86" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" t="s">
+        <v>14</v>
+      </c>
+      <c r="F86" t="s">
+        <v>24</v>
+      </c>
+      <c r="G86" t="s">
+        <v>24</v>
+      </c>
+      <c r="H86" t="s">
+        <v>24</v>
+      </c>
+      <c r="J86" t="s">
+        <v>24</v>
+      </c>
+      <c r="K86" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="87" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B87" t="s">
+        <v>176</v>
+      </c>
+      <c r="C87" t="s">
+        <v>177</v>
+      </c>
+      <c r="D87" t="s">
+        <v>13</v>
+      </c>
+      <c r="E87" t="s">
+        <v>14</v>
+      </c>
+      <c r="F87" t="s">
+        <v>24</v>
+      </c>
+      <c r="G87" t="s">
+        <v>24</v>
+      </c>
+      <c r="H87" t="s">
+        <v>24</v>
+      </c>
+      <c r="J87" t="s">
+        <v>24</v>
+      </c>
+      <c r="K87" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B88" t="s">
+        <v>178</v>
+      </c>
+      <c r="C88" t="s">
+        <v>179</v>
+      </c>
+      <c r="D88" t="s">
+        <v>13</v>
+      </c>
+      <c r="E88" t="s">
+        <v>14</v>
+      </c>
+      <c r="F88" t="s">
+        <v>24</v>
+      </c>
+      <c r="G88" t="s">
+        <v>24</v>
+      </c>
+      <c r="H88" t="s">
+        <v>24</v>
+      </c>
+      <c r="J88" t="s">
+        <v>24</v>
+      </c>
+      <c r="K88" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="89" spans="2:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="B89" t="s">
+        <v>180</v>
+      </c>
+      <c r="C89" t="s">
+        <v>181</v>
+      </c>
+      <c r="D89" t="s">
+        <v>13</v>
+      </c>
+      <c r="E89" t="s">
+        <v>14</v>
+      </c>
+      <c r="F89" t="s">
+        <v>309</v>
+      </c>
+      <c r="G89" t="s">
+        <v>15</v>
+      </c>
+      <c r="H89" t="s">
+        <v>310</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="J89" t="s">
+        <v>20</v>
+      </c>
+      <c r="K89" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="86" spans="2:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="B86" t="s">
+    <row r="90" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B90" t="s">
+        <v>182</v>
+      </c>
+      <c r="C90" t="s">
+        <v>183</v>
+      </c>
+      <c r="D90" t="s">
+        <v>13</v>
+      </c>
+      <c r="E90" t="s">
+        <v>14</v>
+      </c>
+      <c r="F90" t="s">
+        <v>24</v>
+      </c>
+      <c r="G90" t="s">
+        <v>24</v>
+      </c>
+      <c r="H90" t="s">
+        <v>24</v>
+      </c>
+      <c r="J90" t="s">
+        <v>24</v>
+      </c>
+      <c r="K90" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="91" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B91" t="s">
+        <v>184</v>
+      </c>
+      <c r="C91" t="s">
+        <v>185</v>
+      </c>
+      <c r="D91" t="s">
+        <v>13</v>
+      </c>
+      <c r="E91" t="s">
+        <v>14</v>
+      </c>
+      <c r="F91" t="s">
+        <v>24</v>
+      </c>
+      <c r="G91" t="s">
+        <v>24</v>
+      </c>
+      <c r="H91" t="s">
+        <v>24</v>
+      </c>
+      <c r="J91" t="s">
+        <v>24</v>
+      </c>
+      <c r="K91" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B92" t="s">
+        <v>186</v>
+      </c>
+      <c r="C92" t="s">
+        <v>187</v>
+      </c>
+      <c r="D92" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92" t="s">
+        <v>14</v>
+      </c>
+      <c r="F92" t="s">
+        <v>311</v>
+      </c>
+      <c r="G92" t="s">
+        <v>15</v>
+      </c>
+      <c r="H92" t="s">
+        <v>312</v>
+      </c>
+      <c r="I92" t="s">
+        <v>315</v>
+      </c>
+      <c r="J92" t="s">
+        <v>20</v>
+      </c>
+      <c r="K92" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="93" spans="2:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="B93" t="s">
         <v>188</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C93" t="s">
         <v>189</v>
       </c>
-      <c r="D86" t="s">
-        <v>13</v>
-      </c>
-      <c r="E86" t="s">
-        <v>14</v>
-      </c>
-      <c r="F86" s="10" t="s">
+      <c r="D93" t="s">
+        <v>13</v>
+      </c>
+      <c r="E93" t="s">
+        <v>14</v>
+      </c>
+      <c r="F93" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="G86" s="10" t="s">
+      <c r="G93" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H86" s="10" t="s">
+      <c r="H93" s="10" t="s">
         <v>317</v>
       </c>
-      <c r="I86" s="12" t="s">
+      <c r="I93" s="12" t="s">
         <v>318</v>
       </c>
-      <c r="J86" s="10" t="s">
+      <c r="J93" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K86" s="10" t="s">
+      <c r="K93" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="87" spans="2:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="B87" t="s">
+    <row r="94" spans="2:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="B94" t="s">
         <v>190</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C94" t="s">
         <v>191</v>
       </c>
-      <c r="D87" t="s">
-        <v>13</v>
-      </c>
-      <c r="E87" t="s">
-        <v>14</v>
-      </c>
-      <c r="F87" t="s">
+      <c r="D94" t="s">
+        <v>13</v>
+      </c>
+      <c r="E94" t="s">
+        <v>14</v>
+      </c>
+      <c r="F94" t="s">
         <v>319</v>
-      </c>
-      <c r="G87" t="s">
-        <v>15</v>
-      </c>
-      <c r="H87" t="s">
-        <v>320</v>
-      </c>
-      <c r="I87" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="J87" t="s">
-        <v>20</v>
-      </c>
-      <c r="K87" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="88" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B88" t="s">
-        <v>192</v>
-      </c>
-      <c r="C88" t="s">
-        <v>193</v>
-      </c>
-      <c r="D88" t="s">
-        <v>13</v>
-      </c>
-      <c r="E88" t="s">
-        <v>14</v>
-      </c>
-      <c r="F88" s="10" t="s">
-        <v>322</v>
-      </c>
-      <c r="G88" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H88" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="I88" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="J88" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="K88" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="89" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B89" t="s">
-        <v>194</v>
-      </c>
-      <c r="C89" t="s">
-        <v>195</v>
-      </c>
-      <c r="D89" t="s">
-        <v>13</v>
-      </c>
-      <c r="E89" t="s">
-        <v>14</v>
-      </c>
-      <c r="F89" s="14" t="s">
-        <v>324</v>
-      </c>
-      <c r="G89" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="I89" s="12"/>
-      <c r="J89" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="K89" s="10" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="90" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B90" t="s">
-        <v>196</v>
-      </c>
-      <c r="C90" t="s">
-        <v>197</v>
-      </c>
-      <c r="D90" t="s">
-        <v>13</v>
-      </c>
-      <c r="E90" t="s">
-        <v>14</v>
-      </c>
-      <c r="F90" s="14" t="s">
-        <v>326</v>
-      </c>
-      <c r="G90" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="H90" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="I90" s="12"/>
-      <c r="J90" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="K90" s="10" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="91" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B91" t="s">
-        <v>198</v>
-      </c>
-      <c r="C91" t="s">
-        <v>199</v>
-      </c>
-      <c r="D91" t="s">
-        <v>13</v>
-      </c>
-      <c r="E91" t="s">
-        <v>14</v>
-      </c>
-      <c r="F91" s="10" t="s">
-        <v>327</v>
-      </c>
-      <c r="G91" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="I91" s="12"/>
-      <c r="J91" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="K91" s="10" t="s">
-        <v>263</v>
-      </c>
-      <c r="L91" s="10"/>
-    </row>
-    <row r="92" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B92" t="s">
-        <v>200</v>
-      </c>
-      <c r="C92" t="s">
-        <v>201</v>
-      </c>
-      <c r="D92" t="s">
-        <v>13</v>
-      </c>
-      <c r="E92" t="s">
-        <v>14</v>
-      </c>
-      <c r="F92" t="s">
-        <v>24</v>
-      </c>
-      <c r="G92" t="s">
-        <v>24</v>
-      </c>
-      <c r="H92" t="s">
-        <v>24</v>
-      </c>
-      <c r="J92" t="s">
-        <v>24</v>
-      </c>
-      <c r="K92" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="93" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B93" t="s">
-        <v>202</v>
-      </c>
-      <c r="C93" t="s">
-        <v>203</v>
-      </c>
-      <c r="D93" t="s">
-        <v>13</v>
-      </c>
-      <c r="E93" t="s">
-        <v>14</v>
-      </c>
-      <c r="F93" t="s">
-        <v>328</v>
-      </c>
-      <c r="G93" t="s">
-        <v>273</v>
-      </c>
-      <c r="H93" t="s">
-        <v>273</v>
-      </c>
-      <c r="I93" s="3"/>
-      <c r="J93" t="s">
-        <v>20</v>
-      </c>
-      <c r="K93" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="94" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B94" t="s">
-        <v>204</v>
-      </c>
-      <c r="C94" t="s">
-        <v>205</v>
-      </c>
-      <c r="D94" t="s">
-        <v>13</v>
-      </c>
-      <c r="E94" t="s">
-        <v>14</v>
-      </c>
-      <c r="F94" t="s">
-        <v>329</v>
       </c>
       <c r="G94" t="s">
         <v>15</v>
       </c>
       <c r="H94" t="s">
-        <v>330</v>
+        <v>320</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>321</v>
       </c>
       <c r="J94" t="s">
         <v>20</v>
@@ -4328,12 +4414,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="95" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="C95" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="D95" t="s">
         <v>13</v>
@@ -4341,57 +4427,61 @@
       <c r="E95" t="s">
         <v>14</v>
       </c>
-      <c r="F95" t="s">
-        <v>331</v>
-      </c>
-      <c r="G95" t="s">
+      <c r="F95" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="G95" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H95" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="I95" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="J95" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K95" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B96" t="s">
+        <v>194</v>
+      </c>
+      <c r="C96" t="s">
+        <v>195</v>
+      </c>
+      <c r="D96" t="s">
+        <v>13</v>
+      </c>
+      <c r="E96" t="s">
+        <v>14</v>
+      </c>
+      <c r="F96" s="14" t="s">
+        <v>324</v>
+      </c>
+      <c r="G96" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="H95" t="s">
+      <c r="H96" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="J95" t="s">
+      <c r="I96" s="12"/>
+      <c r="J96" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K95" t="s">
+      <c r="K96" s="10" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="96" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B96" t="s">
-        <v>208</v>
-      </c>
-      <c r="C96" t="s">
-        <v>209</v>
-      </c>
-      <c r="D96" t="s">
-        <v>13</v>
-      </c>
-      <c r="E96" t="s">
-        <v>14</v>
-      </c>
-      <c r="F96" t="s">
-        <v>24</v>
-      </c>
-      <c r="G96" t="s">
-        <v>24</v>
-      </c>
-      <c r="H96" t="s">
-        <v>24</v>
-      </c>
-      <c r="J96" t="s">
-        <v>24</v>
-      </c>
-      <c r="K96" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="97" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="C97" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="D97" t="s">
         <v>13</v>
@@ -4399,28 +4489,29 @@
       <c r="E97" t="s">
         <v>14</v>
       </c>
-      <c r="F97" t="s">
-        <v>332</v>
-      </c>
-      <c r="G97" t="s">
+      <c r="F97" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="G97" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="H97" t="s">
+      <c r="H97" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="J97" t="s">
+      <c r="I97" s="12"/>
+      <c r="J97" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K97" t="s">
+      <c r="K97" s="10" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="98" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="C98" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="D98" t="s">
         <v>13</v>
@@ -4428,28 +4519,30 @@
       <c r="E98" t="s">
         <v>14</v>
       </c>
-      <c r="F98" t="s">
-        <v>333</v>
-      </c>
-      <c r="G98" t="s">
+      <c r="F98" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="G98" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="H98" t="s">
+      <c r="H98" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="J98" t="s">
+      <c r="I98" s="12"/>
+      <c r="J98" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K98" t="s">
+      <c r="K98" s="10" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="99" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L98" s="10"/>
+    </row>
+    <row r="99" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="C99" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="D99" t="s">
         <v>13</v>
@@ -4473,12 +4566,12 @@
         <v>348</v>
       </c>
     </row>
-    <row r="100" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="C100" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="D100" t="s">
         <v>13</v>
@@ -4487,27 +4580,28 @@
         <v>14</v>
       </c>
       <c r="F100" t="s">
-        <v>24</v>
+        <v>328</v>
       </c>
       <c r="G100" t="s">
-        <v>24</v>
+        <v>273</v>
       </c>
       <c r="H100" t="s">
-        <v>24</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="I100" s="3"/>
       <c r="J100" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K100" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="101" spans="2:11" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="101" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C101" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="D101" t="s">
         <v>13</v>
@@ -4516,317 +4610,317 @@
         <v>14</v>
       </c>
       <c r="F101" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G101" t="s">
-        <v>273</v>
+        <v>15</v>
       </c>
       <c r="H101" t="s">
-        <v>273</v>
+        <v>330</v>
       </c>
       <c r="J101" t="s">
         <v>20</v>
       </c>
       <c r="K101" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="102" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B102" t="s">
+        <v>206</v>
+      </c>
+      <c r="C102" t="s">
+        <v>207</v>
+      </c>
+      <c r="D102" t="s">
+        <v>13</v>
+      </c>
+      <c r="E102" t="s">
+        <v>14</v>
+      </c>
+      <c r="F102" t="s">
+        <v>331</v>
+      </c>
+      <c r="G102" t="s">
+        <v>273</v>
+      </c>
+      <c r="H102" t="s">
+        <v>273</v>
+      </c>
+      <c r="J102" t="s">
+        <v>20</v>
+      </c>
+      <c r="K102" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="102" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B102" t="s">
+    <row r="103" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B103" t="s">
+        <v>208</v>
+      </c>
+      <c r="C103" t="s">
+        <v>209</v>
+      </c>
+      <c r="D103" t="s">
+        <v>13</v>
+      </c>
+      <c r="E103" t="s">
+        <v>14</v>
+      </c>
+      <c r="F103" t="s">
+        <v>24</v>
+      </c>
+      <c r="G103" t="s">
+        <v>24</v>
+      </c>
+      <c r="H103" t="s">
+        <v>24</v>
+      </c>
+      <c r="J103" t="s">
+        <v>24</v>
+      </c>
+      <c r="K103" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="104" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B104" t="s">
+        <v>210</v>
+      </c>
+      <c r="C104" t="s">
+        <v>211</v>
+      </c>
+      <c r="D104" t="s">
+        <v>13</v>
+      </c>
+      <c r="E104" t="s">
+        <v>14</v>
+      </c>
+      <c r="F104" t="s">
+        <v>332</v>
+      </c>
+      <c r="G104" t="s">
+        <v>273</v>
+      </c>
+      <c r="H104" t="s">
+        <v>273</v>
+      </c>
+      <c r="J104" t="s">
+        <v>20</v>
+      </c>
+      <c r="K104" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="105" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B105" t="s">
+        <v>212</v>
+      </c>
+      <c r="C105" t="s">
+        <v>213</v>
+      </c>
+      <c r="D105" t="s">
+        <v>13</v>
+      </c>
+      <c r="E105" t="s">
+        <v>14</v>
+      </c>
+      <c r="F105" t="s">
+        <v>333</v>
+      </c>
+      <c r="G105" t="s">
+        <v>273</v>
+      </c>
+      <c r="H105" t="s">
+        <v>273</v>
+      </c>
+      <c r="J105" t="s">
+        <v>20</v>
+      </c>
+      <c r="K105" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="106" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B106" t="s">
+        <v>214</v>
+      </c>
+      <c r="C106" t="s">
+        <v>215</v>
+      </c>
+      <c r="D106" t="s">
+        <v>13</v>
+      </c>
+      <c r="E106" t="s">
+        <v>14</v>
+      </c>
+      <c r="F106" t="s">
+        <v>24</v>
+      </c>
+      <c r="G106" t="s">
+        <v>24</v>
+      </c>
+      <c r="H106" t="s">
+        <v>24</v>
+      </c>
+      <c r="J106" t="s">
+        <v>24</v>
+      </c>
+      <c r="K106" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="107" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B107" t="s">
+        <v>216</v>
+      </c>
+      <c r="C107" t="s">
+        <v>217</v>
+      </c>
+      <c r="D107" t="s">
+        <v>13</v>
+      </c>
+      <c r="E107" t="s">
+        <v>14</v>
+      </c>
+      <c r="F107" t="s">
+        <v>24</v>
+      </c>
+      <c r="G107" t="s">
+        <v>24</v>
+      </c>
+      <c r="H107" t="s">
+        <v>24</v>
+      </c>
+      <c r="J107" t="s">
+        <v>24</v>
+      </c>
+      <c r="K107" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="108" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B108" t="s">
+        <v>218</v>
+      </c>
+      <c r="C108" t="s">
+        <v>219</v>
+      </c>
+      <c r="D108" t="s">
+        <v>13</v>
+      </c>
+      <c r="E108" t="s">
+        <v>14</v>
+      </c>
+      <c r="F108" t="s">
+        <v>334</v>
+      </c>
+      <c r="G108" t="s">
+        <v>273</v>
+      </c>
+      <c r="H108" t="s">
+        <v>273</v>
+      </c>
+      <c r="J108" t="s">
+        <v>20</v>
+      </c>
+      <c r="K108" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="109" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B109" t="s">
         <v>220</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C109" t="s">
         <v>221</v>
       </c>
-      <c r="D102" t="s">
-        <v>13</v>
-      </c>
-      <c r="E102" t="s">
-        <v>14</v>
-      </c>
-      <c r="F102" t="s">
-        <v>24</v>
-      </c>
-      <c r="G102" t="s">
-        <v>24</v>
-      </c>
-      <c r="H102" t="s">
-        <v>24</v>
-      </c>
-      <c r="J102" t="s">
-        <v>24</v>
-      </c>
-      <c r="K102" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="103" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B103" t="s">
+      <c r="D109" t="s">
+        <v>13</v>
+      </c>
+      <c r="E109" t="s">
+        <v>14</v>
+      </c>
+      <c r="F109" t="s">
+        <v>24</v>
+      </c>
+      <c r="G109" t="s">
+        <v>24</v>
+      </c>
+      <c r="H109" t="s">
+        <v>24</v>
+      </c>
+      <c r="J109" t="s">
+        <v>24</v>
+      </c>
+      <c r="K109" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="110" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B110" t="s">
         <v>222</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C110" t="s">
         <v>223</v>
       </c>
-      <c r="D103" t="s">
-        <v>13</v>
-      </c>
-      <c r="E103" t="s">
-        <v>14</v>
-      </c>
-      <c r="F103" t="s">
-        <v>24</v>
-      </c>
-      <c r="G103" t="s">
-        <v>24</v>
-      </c>
-      <c r="H103" t="s">
-        <v>24</v>
-      </c>
-      <c r="J103" t="s">
-        <v>24</v>
-      </c>
-      <c r="K103" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="104" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B104" t="s">
+      <c r="D110" t="s">
+        <v>13</v>
+      </c>
+      <c r="E110" t="s">
+        <v>14</v>
+      </c>
+      <c r="F110" t="s">
+        <v>24</v>
+      </c>
+      <c r="G110" t="s">
+        <v>24</v>
+      </c>
+      <c r="H110" t="s">
+        <v>24</v>
+      </c>
+      <c r="J110" t="s">
+        <v>24</v>
+      </c>
+      <c r="K110" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="111" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B111" t="s">
         <v>224</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C111" t="s">
         <v>225</v>
       </c>
-      <c r="D104" t="s">
-        <v>13</v>
-      </c>
-      <c r="E104" t="s">
-        <v>14</v>
-      </c>
-      <c r="F104" t="s">
-        <v>24</v>
-      </c>
-      <c r="G104" t="s">
-        <v>24</v>
-      </c>
-      <c r="H104" t="s">
-        <v>24</v>
-      </c>
-      <c r="J104" t="s">
-        <v>24</v>
-      </c>
-      <c r="K104" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="105" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B105" t="s">
+      <c r="D111" t="s">
+        <v>13</v>
+      </c>
+      <c r="E111" t="s">
+        <v>14</v>
+      </c>
+      <c r="F111" t="s">
+        <v>24</v>
+      </c>
+      <c r="G111" t="s">
+        <v>24</v>
+      </c>
+      <c r="H111" t="s">
+        <v>24</v>
+      </c>
+      <c r="J111" t="s">
+        <v>24</v>
+      </c>
+      <c r="K111" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="112" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B112" t="s">
         <v>226</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C112" t="s">
         <v>227</v>
-      </c>
-      <c r="D105" t="s">
-        <v>13</v>
-      </c>
-      <c r="E105" t="s">
-        <v>14</v>
-      </c>
-      <c r="F105" t="s">
-        <v>24</v>
-      </c>
-      <c r="G105" t="s">
-        <v>24</v>
-      </c>
-      <c r="H105" t="s">
-        <v>24</v>
-      </c>
-      <c r="J105" t="s">
-        <v>24</v>
-      </c>
-      <c r="K105" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="106" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B106" t="s">
-        <v>228</v>
-      </c>
-      <c r="C106" t="s">
-        <v>229</v>
-      </c>
-      <c r="D106" t="s">
-        <v>13</v>
-      </c>
-      <c r="E106" t="s">
-        <v>14</v>
-      </c>
-      <c r="F106" t="s">
-        <v>24</v>
-      </c>
-      <c r="G106" t="s">
-        <v>24</v>
-      </c>
-      <c r="H106" t="s">
-        <v>24</v>
-      </c>
-      <c r="J106" t="s">
-        <v>24</v>
-      </c>
-      <c r="K106" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="107" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B107" t="s">
-        <v>230</v>
-      </c>
-      <c r="C107" t="s">
-        <v>231</v>
-      </c>
-      <c r="D107" t="s">
-        <v>13</v>
-      </c>
-      <c r="E107" t="s">
-        <v>14</v>
-      </c>
-      <c r="F107" t="s">
-        <v>24</v>
-      </c>
-      <c r="G107" t="s">
-        <v>24</v>
-      </c>
-      <c r="H107" t="s">
-        <v>24</v>
-      </c>
-      <c r="J107" t="s">
-        <v>24</v>
-      </c>
-      <c r="K107" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="108" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B108" t="s">
-        <v>232</v>
-      </c>
-      <c r="C108" t="s">
-        <v>233</v>
-      </c>
-      <c r="D108" t="s">
-        <v>13</v>
-      </c>
-      <c r="E108" t="s">
-        <v>14</v>
-      </c>
-      <c r="F108" t="s">
-        <v>24</v>
-      </c>
-      <c r="G108" t="s">
-        <v>24</v>
-      </c>
-      <c r="H108" t="s">
-        <v>24</v>
-      </c>
-      <c r="J108" t="s">
-        <v>24</v>
-      </c>
-      <c r="K108" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="109" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B109" t="s">
-        <v>234</v>
-      </c>
-      <c r="C109" t="s">
-        <v>235</v>
-      </c>
-      <c r="D109" t="s">
-        <v>13</v>
-      </c>
-      <c r="E109" t="s">
-        <v>14</v>
-      </c>
-      <c r="F109" t="s">
-        <v>24</v>
-      </c>
-      <c r="G109" t="s">
-        <v>24</v>
-      </c>
-      <c r="H109" t="s">
-        <v>24</v>
-      </c>
-      <c r="J109" t="s">
-        <v>24</v>
-      </c>
-      <c r="K109" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="110" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B110" t="s">
-        <v>236</v>
-      </c>
-      <c r="C110" t="s">
-        <v>237</v>
-      </c>
-      <c r="D110" t="s">
-        <v>13</v>
-      </c>
-      <c r="E110" t="s">
-        <v>14</v>
-      </c>
-      <c r="F110" t="s">
-        <v>24</v>
-      </c>
-      <c r="G110" t="s">
-        <v>24</v>
-      </c>
-      <c r="H110" t="s">
-        <v>24</v>
-      </c>
-      <c r="J110" t="s">
-        <v>24</v>
-      </c>
-      <c r="K110" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="111" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B111" t="s">
-        <v>238</v>
-      </c>
-      <c r="C111" t="s">
-        <v>239</v>
-      </c>
-      <c r="D111" t="s">
-        <v>13</v>
-      </c>
-      <c r="E111" t="s">
-        <v>14</v>
-      </c>
-      <c r="F111" t="s">
-        <v>24</v>
-      </c>
-      <c r="G111" t="s">
-        <v>24</v>
-      </c>
-      <c r="H111" t="s">
-        <v>24</v>
-      </c>
-      <c r="J111" t="s">
-        <v>24</v>
-      </c>
-      <c r="K111" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B112" t="s">
-        <v>240</v>
-      </c>
-      <c r="C112" t="s">
-        <v>241</v>
       </c>
       <c r="D112" t="s">
         <v>13</v>
@@ -4852,10 +4946,10 @@
     </row>
     <row r="113" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="C113" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="D113" t="s">
         <v>13</v>
@@ -4881,10 +4975,10 @@
     </row>
     <row r="114" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="C114" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="D114" t="s">
         <v>13</v>
@@ -4910,10 +5004,10 @@
     </row>
     <row r="115" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="C115" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="D115" t="s">
         <v>13</v>
@@ -4939,10 +5033,10 @@
     </row>
     <row r="116" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="C116" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="D116" t="s">
         <v>13</v>
@@ -4968,10 +5062,10 @@
     </row>
     <row r="117" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="C117" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="D117" t="s">
         <v>13</v>
@@ -4997,10 +5091,10 @@
     </row>
     <row r="118" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C118" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D118" t="s">
         <v>13</v>
@@ -5024,12 +5118,12 @@
         <v>348</v>
       </c>
     </row>
-    <row r="119" spans="2:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="C119" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D119" t="s">
         <v>13</v>
@@ -5038,30 +5132,27 @@
         <v>14</v>
       </c>
       <c r="F119" t="s">
-        <v>335</v>
+        <v>24</v>
       </c>
       <c r="G119" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H119" t="s">
-        <v>336</v>
-      </c>
-      <c r="I119" s="3" t="s">
-        <v>337</v>
+        <v>24</v>
       </c>
       <c r="J119" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K119" t="s">
-        <v>21</v>
+        <v>348</v>
       </c>
     </row>
     <row r="120" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="C120" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="D120" t="s">
         <v>13</v>
@@ -5087,33 +5178,239 @@
     </row>
     <row r="121" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
+        <v>244</v>
+      </c>
+      <c r="C121" t="s">
+        <v>245</v>
+      </c>
+      <c r="D121" t="s">
+        <v>13</v>
+      </c>
+      <c r="E121" t="s">
+        <v>14</v>
+      </c>
+      <c r="F121" t="s">
+        <v>24</v>
+      </c>
+      <c r="G121" t="s">
+        <v>24</v>
+      </c>
+      <c r="H121" t="s">
+        <v>24</v>
+      </c>
+      <c r="J121" t="s">
+        <v>24</v>
+      </c>
+      <c r="K121" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="122" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B122" t="s">
+        <v>246</v>
+      </c>
+      <c r="C122" t="s">
+        <v>247</v>
+      </c>
+      <c r="D122" t="s">
+        <v>13</v>
+      </c>
+      <c r="E122" t="s">
+        <v>14</v>
+      </c>
+      <c r="F122" t="s">
+        <v>24</v>
+      </c>
+      <c r="G122" t="s">
+        <v>24</v>
+      </c>
+      <c r="H122" t="s">
+        <v>24</v>
+      </c>
+      <c r="J122" t="s">
+        <v>24</v>
+      </c>
+      <c r="K122" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="123" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B123" t="s">
+        <v>248</v>
+      </c>
+      <c r="C123" t="s">
+        <v>249</v>
+      </c>
+      <c r="D123" t="s">
+        <v>13</v>
+      </c>
+      <c r="E123" t="s">
+        <v>14</v>
+      </c>
+      <c r="F123" t="s">
+        <v>24</v>
+      </c>
+      <c r="G123" t="s">
+        <v>24</v>
+      </c>
+      <c r="H123" t="s">
+        <v>24</v>
+      </c>
+      <c r="J123" t="s">
+        <v>24</v>
+      </c>
+      <c r="K123" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="124" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B124" t="s">
+        <v>250</v>
+      </c>
+      <c r="C124" t="s">
+        <v>251</v>
+      </c>
+      <c r="D124" t="s">
+        <v>13</v>
+      </c>
+      <c r="E124" t="s">
+        <v>14</v>
+      </c>
+      <c r="F124" t="s">
+        <v>24</v>
+      </c>
+      <c r="G124" t="s">
+        <v>24</v>
+      </c>
+      <c r="H124" t="s">
+        <v>24</v>
+      </c>
+      <c r="J124" t="s">
+        <v>24</v>
+      </c>
+      <c r="K124" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="125" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B125" t="s">
+        <v>252</v>
+      </c>
+      <c r="C125" t="s">
+        <v>253</v>
+      </c>
+      <c r="D125" t="s">
+        <v>13</v>
+      </c>
+      <c r="E125" t="s">
+        <v>14</v>
+      </c>
+      <c r="F125" t="s">
+        <v>24</v>
+      </c>
+      <c r="G125" t="s">
+        <v>24</v>
+      </c>
+      <c r="H125" t="s">
+        <v>24</v>
+      </c>
+      <c r="J125" t="s">
+        <v>24</v>
+      </c>
+      <c r="K125" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="126" spans="2:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="B126" t="s">
+        <v>254</v>
+      </c>
+      <c r="C126" t="s">
+        <v>255</v>
+      </c>
+      <c r="D126" t="s">
+        <v>13</v>
+      </c>
+      <c r="E126" t="s">
+        <v>14</v>
+      </c>
+      <c r="F126" t="s">
+        <v>335</v>
+      </c>
+      <c r="G126" t="s">
+        <v>15</v>
+      </c>
+      <c r="H126" t="s">
+        <v>336</v>
+      </c>
+      <c r="I126" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="J126" t="s">
+        <v>20</v>
+      </c>
+      <c r="K126" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B127" t="s">
+        <v>256</v>
+      </c>
+      <c r="C127" t="s">
+        <v>257</v>
+      </c>
+      <c r="D127" t="s">
+        <v>13</v>
+      </c>
+      <c r="E127" t="s">
+        <v>14</v>
+      </c>
+      <c r="F127" t="s">
+        <v>24</v>
+      </c>
+      <c r="G127" t="s">
+        <v>24</v>
+      </c>
+      <c r="H127" t="s">
+        <v>24</v>
+      </c>
+      <c r="J127" t="s">
+        <v>24</v>
+      </c>
+      <c r="K127" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="128" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B128" t="s">
         <v>258</v>
       </c>
-      <c r="C121" t="s">
+      <c r="C128" t="s">
         <v>259</v>
       </c>
-      <c r="D121" t="s">
+      <c r="D128" t="s">
         <v>260</v>
       </c>
-      <c r="E121" t="s">
-        <v>14</v>
-      </c>
-      <c r="F121" s="4" t="s">
+      <c r="E128" t="s">
+        <v>14</v>
+      </c>
+      <c r="F128" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="G121" s="5" t="s">
+      <c r="G128" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="H121" s="6">
+      <c r="H128" s="6">
         <v>1</v>
       </c>
-      <c r="I121" s="7" t="s">
+      <c r="I128" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="J121" s="8" t="s">
+      <c r="J128" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="K121" s="8" t="s">
+      <c r="K128" s="8" t="s">
         <v>263</v>
       </c>
     </row>
@@ -5124,6 +5421,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Zeit xmlns="b63cdcf7-47fa-43f6-87e5-23b415b5c413" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b63cdcf7-47fa-43f6-87e5-23b415b5c413">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="12535b08-222e-45d2-b6db-15019f1afee6" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100B1DC67C611DD5E4D81775F9F3E26A7B2" ma:contentTypeVersion="16" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="7f379a5812b480a74f9d031be5f88a83">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b63cdcf7-47fa-43f6-87e5-23b415b5c413" xmlns:ns3="12535b08-222e-45d2-b6db-15019f1afee6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dbce1e37d7de67e1c835013ca0ee7a7c" ns2:_="" ns3:_="">
     <xsd:import namespace="b63cdcf7-47fa-43f6-87e5-23b415b5c413"/>
@@ -5364,28 +5682,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7C1076D-2C61-4BAC-A503-5A4B20CD35B7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="b63cdcf7-47fa-43f6-87e5-23b415b5c413"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="12535b08-222e-45d2-b6db-15019f1afee6"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Zeit xmlns="b63cdcf7-47fa-43f6-87e5-23b415b5c413" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b63cdcf7-47fa-43f6-87e5-23b415b5c413">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="12535b08-222e-45d2-b6db-15019f1afee6" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70A53FE4-D237-4764-9B07-7D2AFF4EC446}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EDAC40C-4E49-457D-B6B8-71BBCE94E8A2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5402,29 +5724,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70A53FE4-D237-4764-9B07-7D2AFF4EC446}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7C1076D-2C61-4BAC-A503-5A4B20CD35B7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="b63cdcf7-47fa-43f6-87e5-23b415b5c413"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="12535b08-222e-45d2-b6db-15019f1afee6"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/analyst/Franzi/rmonize/data_proc_elem/DPE_DEGS1_FRANZI.xlsx
+++ b/analyst/Franzi/rmonize/data_proc_elem/DPE_DEGS1_FRANZI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Projekte\NFDI4Health\TA5\Pilotprojekte\Harmonisierung\HarmonizR\use-cases-harmonisation\analyst\Franzi\rmonize\data_proc_elem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Franzi\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12ECF6FB-D33C-48E1-A501-FDF43EAB843A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0A7CDC-9D01-4312-AF99-AC3E020E9DF0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,17 +20,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -39,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="349">
   <si>
     <t>index</t>
   </si>
@@ -843,9 +832,6 @@
   </si>
   <si>
     <t>Summe aus gebratenen Kartoffeln + gekochten Kartoffeln + Pommes frites</t>
-  </si>
-  <si>
-    <t>mrgem; mggem</t>
   </si>
   <si>
     <t>mrgem+mggem</t>
@@ -1089,86 +1075,14 @@
     <t>unavailable</t>
   </si>
   <si>
-    <t>SEX</t>
-  </si>
-  <si>
-    <t>AGE_BASE</t>
-  </si>
-  <si>
-    <t>EDU_LEVEL</t>
-  </si>
-  <si>
-    <t>TOT_PA_QX</t>
-  </si>
-  <si>
-    <t>SMOKE_ST</t>
-  </si>
-  <si>
-    <t>BMI</t>
-  </si>
-  <si>
-    <t>ENERGY</t>
-  </si>
-  <si>
-    <t>sex</t>
-  </si>
-  <si>
-    <t>Sex</t>
-  </si>
-  <si>
-    <t>Age at exposure measure [years]</t>
-  </si>
-  <si>
-    <t>Highest level of education [ISCED 2011]</t>
-  </si>
-  <si>
-    <t>Physical activity from questionnaire data [MET-hr/day]</t>
-  </si>
-  <si>
-    <t>Smoking status</t>
-  </si>
-  <si>
-    <t>Body Mass Index at baseline [kg/m²]</t>
-  </si>
-  <si>
-    <t>Energy intake [kcal/d]</t>
-  </si>
-  <si>
-    <t>age</t>
-  </si>
-  <si>
-    <t>Rauchstatus in 3 Kategorien</t>
-  </si>
-  <si>
-    <t>SDisced97z</t>
-  </si>
-  <si>
-    <t>Usbmi</t>
-  </si>
-  <si>
-    <t>KAempf_k</t>
-  </si>
-  <si>
-    <t>recode</t>
-  </si>
-  <si>
-    <t>RCstat_k</t>
-  </si>
-  <si>
-    <t>Kategorien siehe DD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1=3;2=2;3=1;ELSE=4) </t>
-  </si>
-  <si>
-    <t>tba</t>
+    <t>mrgem;mggem</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1217,13 +1131,6 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1251,7 +1158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1285,7 +1192,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1304,9 +1210,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1344,9 +1250,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1379,9 +1285,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1414,9 +1337,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1590,7 +1530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L128"/>
+  <dimension ref="A1:L121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
@@ -1640,42 +1580,44 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>349</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>357</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>260</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>356</v>
+        <v>265</v>
       </c>
       <c r="G2" t="s">
-        <v>273</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>273</v>
-      </c>
-      <c r="I2" s="3"/>
+        <v>266</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>346</v>
+      </c>
       <c r="J2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>350</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>358</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
@@ -1684,122 +1626,120 @@
         <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>364</v>
+        <v>265</v>
       </c>
       <c r="G3" t="s">
-        <v>273</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>273</v>
-      </c>
-      <c r="I3" s="3"/>
+        <v>266</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>267</v>
+      </c>
       <c r="J3" t="s">
         <v>20</v>
       </c>
       <c r="K3" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>351</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>359</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>260</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>366</v>
+        <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>369</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>373</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>371</v>
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>24</v>
       </c>
       <c r="J4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" t="s">
+        <v>348</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>268</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="J5" t="s">
         <v>20</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>352</v>
-      </c>
-      <c r="C5" t="s">
-        <v>360</v>
-      </c>
-      <c r="D5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" t="s">
-        <v>368</v>
-      </c>
-      <c r="G5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="J5" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>353</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>361</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>260</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
         <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>370</v>
+        <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>369</v>
+        <v>24</v>
       </c>
       <c r="H6" t="s">
-        <v>372</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>365</v>
+        <v>24</v>
       </c>
       <c r="J6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>354</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>362</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
@@ -1808,28 +1748,27 @@
         <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>367</v>
+        <v>24</v>
       </c>
       <c r="G7" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="H7" t="s">
-        <v>273</v>
-      </c>
-      <c r="I7" s="3"/>
+        <v>24</v>
+      </c>
       <c r="J7" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K7" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>355</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>363</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
         <v>13</v>
@@ -1846,20 +1785,19 @@
       <c r="H8" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="3"/>
       <c r="J8" t="s">
         <v>24</v>
       </c>
       <c r="K8" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
         <v>13</v>
@@ -1868,30 +1806,27 @@
         <v>14</v>
       </c>
       <c r="F9" t="s">
-        <v>265</v>
+        <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H9" t="s">
-        <v>266</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>347</v>
+        <v>24</v>
       </c>
       <c r="J9" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
         <v>13</v>
@@ -1900,30 +1835,27 @@
         <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>265</v>
+        <v>24</v>
       </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H10" t="s">
-        <v>266</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>267</v>
+        <v>24</v>
       </c>
       <c r="J10" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K10" t="s">
-        <v>21</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
@@ -1944,15 +1876,15 @@
         <v>24</v>
       </c>
       <c r="K11" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
         <v>13</v>
@@ -1961,30 +1893,27 @@
         <v>14</v>
       </c>
       <c r="F12" t="s">
-        <v>268</v>
+        <v>24</v>
       </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H12" t="s">
-        <v>269</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>270</v>
+        <v>24</v>
       </c>
       <c r="J12" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K12" t="s">
-        <v>21</v>
+        <v>347</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
         <v>13</v>
@@ -2005,15 +1934,15 @@
         <v>24</v>
       </c>
       <c r="K13" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
         <v>13</v>
@@ -2034,15 +1963,15 @@
         <v>24</v>
       </c>
       <c r="K14" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
         <v>13</v>
@@ -2051,27 +1980,30 @@
         <v>14</v>
       </c>
       <c r="F15" t="s">
-        <v>24</v>
+        <v>270</v>
       </c>
       <c r="G15" t="s">
-        <v>24</v>
+        <v>272</v>
       </c>
       <c r="H15" t="s">
-        <v>24</v>
+        <v>272</v>
+      </c>
+      <c r="I15" t="s">
+        <v>271</v>
       </c>
       <c r="J15" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K15" t="s">
-        <v>348</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
         <v>13</v>
@@ -2092,15 +2024,15 @@
         <v>24</v>
       </c>
       <c r="K16" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="30" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
         <v>13</v>
@@ -2109,27 +2041,30 @@
         <v>14</v>
       </c>
       <c r="F17" t="s">
-        <v>24</v>
+        <v>274</v>
       </c>
       <c r="G17" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>24</v>
+        <v>275</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>276</v>
       </c>
       <c r="J17" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K17" t="s">
-        <v>348</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D18" t="s">
         <v>13</v>
@@ -2138,27 +2073,28 @@
         <v>14</v>
       </c>
       <c r="F18" t="s">
-        <v>24</v>
+        <v>277</v>
       </c>
       <c r="G18" t="s">
-        <v>24</v>
+        <v>272</v>
       </c>
       <c r="H18" t="s">
-        <v>24</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="I18" s="9"/>
       <c r="J18" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K18" t="s">
-        <v>348</v>
+        <v>263</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
         <v>13</v>
@@ -2167,27 +2103,27 @@
         <v>14</v>
       </c>
       <c r="F19" t="s">
-        <v>24</v>
+        <v>278</v>
       </c>
       <c r="G19" t="s">
-        <v>24</v>
+        <v>272</v>
       </c>
       <c r="H19" t="s">
-        <v>24</v>
+        <v>272</v>
       </c>
       <c r="J19" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K19" t="s">
-        <v>348</v>
+        <v>263</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C20" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
         <v>13</v>
@@ -2196,27 +2132,27 @@
         <v>14</v>
       </c>
       <c r="F20" t="s">
-        <v>24</v>
+        <v>273</v>
       </c>
       <c r="G20" t="s">
-        <v>24</v>
+        <v>272</v>
       </c>
       <c r="H20" t="s">
-        <v>24</v>
+        <v>272</v>
       </c>
       <c r="J20" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K20" t="s">
-        <v>348</v>
+        <v>263</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D21" t="s">
         <v>13</v>
@@ -2237,15 +2173,15 @@
         <v>24</v>
       </c>
       <c r="K21" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D22" t="s">
         <v>13</v>
@@ -2253,31 +2189,31 @@
       <c r="E22" t="s">
         <v>14</v>
       </c>
-      <c r="F22" t="s">
-        <v>271</v>
-      </c>
-      <c r="G22" t="s">
-        <v>273</v>
-      </c>
-      <c r="H22" t="s">
-        <v>273</v>
+      <c r="F22" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>338</v>
       </c>
       <c r="I22" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
       <c r="J22" t="s">
         <v>20</v>
       </c>
       <c r="K22" t="s">
-        <v>263</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="D23" t="s">
         <v>13</v>
@@ -2286,27 +2222,27 @@
         <v>14</v>
       </c>
       <c r="F23" t="s">
-        <v>24</v>
+        <v>279</v>
       </c>
       <c r="G23" t="s">
-        <v>24</v>
+        <v>272</v>
       </c>
       <c r="H23" t="s">
-        <v>24</v>
+        <v>272</v>
       </c>
       <c r="J23" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K23" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" ht="30" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="C24" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D24" t="s">
         <v>13</v>
@@ -2315,30 +2251,27 @@
         <v>14</v>
       </c>
       <c r="F24" t="s">
-        <v>275</v>
+        <v>24</v>
       </c>
       <c r="G24" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H24" t="s">
-        <v>276</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>277</v>
+        <v>24</v>
       </c>
       <c r="J24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K24" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" ht="60" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D25" t="s">
         <v>13</v>
@@ -2346,29 +2279,32 @@
       <c r="E25" t="s">
         <v>14</v>
       </c>
-      <c r="F25" t="s">
-        <v>278</v>
-      </c>
-      <c r="G25" t="s">
-        <v>273</v>
-      </c>
-      <c r="H25" t="s">
-        <v>273</v>
-      </c>
-      <c r="I25" s="9"/>
-      <c r="J25" t="s">
-        <v>20</v>
-      </c>
-      <c r="K25" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="F25" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L25" s="10"/>
+    </row>
+    <row r="26" spans="2:12" ht="30" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D26" t="s">
         <v>13</v>
@@ -2376,28 +2312,32 @@
       <c r="E26" t="s">
         <v>14</v>
       </c>
-      <c r="F26" t="s">
-        <v>279</v>
-      </c>
-      <c r="G26" t="s">
-        <v>273</v>
-      </c>
-      <c r="H26" t="s">
-        <v>273</v>
-      </c>
-      <c r="J26" t="s">
-        <v>20</v>
-      </c>
-      <c r="K26" t="s">
-        <v>263</v>
-      </c>
+      <c r="F26" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="K26" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L26" s="10"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D27" t="s">
         <v>13</v>
@@ -2405,28 +2345,30 @@
       <c r="E27" t="s">
         <v>14</v>
       </c>
-      <c r="F27" t="s">
-        <v>274</v>
-      </c>
-      <c r="G27" t="s">
-        <v>273</v>
-      </c>
-      <c r="H27" t="s">
-        <v>273</v>
-      </c>
-      <c r="J27" t="s">
+      <c r="F27" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="I27" s="11"/>
+      <c r="J27" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K27" t="s">
+      <c r="K27" s="10" t="s">
         <v>263</v>
       </c>
+      <c r="L27" s="10"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C28" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="D28" t="s">
         <v>13</v>
@@ -2447,15 +2389,15 @@
         <v>24</v>
       </c>
       <c r="K28" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="C29" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="D29" t="s">
         <v>13</v>
@@ -2463,31 +2405,28 @@
       <c r="E29" t="s">
         <v>14</v>
       </c>
-      <c r="F29" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>339</v>
-      </c>
-      <c r="I29" t="s">
-        <v>340</v>
+      <c r="F29" t="s">
+        <v>24</v>
+      </c>
+      <c r="G29" t="s">
+        <v>24</v>
+      </c>
+      <c r="H29" t="s">
+        <v>24</v>
       </c>
       <c r="J29" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K29" t="s">
-        <v>21</v>
+        <v>347</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="C30" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="D30" t="s">
         <v>13</v>
@@ -2496,27 +2435,27 @@
         <v>14</v>
       </c>
       <c r="F30" t="s">
-        <v>280</v>
+        <v>24</v>
       </c>
       <c r="G30" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="H30" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="J30" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K30" t="s">
-        <v>263</v>
+        <v>347</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C31" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="D31" t="s">
         <v>13</v>
@@ -2537,15 +2476,15 @@
         <v>24</v>
       </c>
       <c r="K31" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12" ht="60" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C32" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="D32" t="s">
         <v>13</v>
@@ -2553,32 +2492,28 @@
       <c r="E32" t="s">
         <v>14</v>
       </c>
-      <c r="F32" s="10" t="s">
-        <v>281</v>
-      </c>
-      <c r="G32" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="H32" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="I32" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="J32" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="K32" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="L32" s="10"/>
-    </row>
-    <row r="33" spans="2:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="F32" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" t="s">
+        <v>24</v>
+      </c>
+      <c r="H32" t="s">
+        <v>24</v>
+      </c>
+      <c r="J32" t="s">
+        <v>24</v>
+      </c>
+      <c r="K32" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="C33" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="D33" t="s">
         <v>13</v>
@@ -2586,32 +2521,28 @@
       <c r="E33" t="s">
         <v>14</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="I33" s="16" t="s">
-        <v>346</v>
-      </c>
-      <c r="J33" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="K33" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="L33" s="10"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="F33" t="s">
+        <v>24</v>
+      </c>
+      <c r="G33" t="s">
+        <v>24</v>
+      </c>
+      <c r="H33" t="s">
+        <v>24</v>
+      </c>
+      <c r="J33" t="s">
+        <v>24</v>
+      </c>
+      <c r="K33" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C34" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="D34" t="s">
         <v>13</v>
@@ -2619,204 +2550,211 @@
       <c r="E34" t="s">
         <v>14</v>
       </c>
-      <c r="F34" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="H34" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="I34" s="11"/>
-      <c r="J34" s="10" t="s">
+      <c r="F34" t="s">
+        <v>24</v>
+      </c>
+      <c r="G34" t="s">
+        <v>24</v>
+      </c>
+      <c r="H34" t="s">
+        <v>24</v>
+      </c>
+      <c r="J34" t="s">
+        <v>24</v>
+      </c>
+      <c r="K34" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" t="s">
+        <v>86</v>
+      </c>
+      <c r="D35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35" t="s">
+        <v>284</v>
+      </c>
+      <c r="G35" t="s">
+        <v>15</v>
+      </c>
+      <c r="H35" t="s">
+        <v>283</v>
+      </c>
+      <c r="I35" t="s">
+        <v>285</v>
+      </c>
+      <c r="J35" t="s">
         <v>20</v>
       </c>
-      <c r="K34" s="10" t="s">
+      <c r="K35" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>87</v>
+      </c>
+      <c r="C36" t="s">
+        <v>88</v>
+      </c>
+      <c r="D36" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" t="s">
+        <v>14</v>
+      </c>
+      <c r="F36" t="s">
+        <v>286</v>
+      </c>
+      <c r="G36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" t="s">
+        <v>287</v>
+      </c>
+      <c r="I36" t="s">
+        <v>288</v>
+      </c>
+      <c r="J36" t="s">
+        <v>20</v>
+      </c>
+      <c r="K36" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" t="s">
+        <v>90</v>
+      </c>
+      <c r="D37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F37" t="s">
+        <v>24</v>
+      </c>
+      <c r="G37" t="s">
+        <v>24</v>
+      </c>
+      <c r="H37" t="s">
+        <v>24</v>
+      </c>
+      <c r="J37" t="s">
+        <v>24</v>
+      </c>
+      <c r="K37" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" t="s">
+        <v>92</v>
+      </c>
+      <c r="D38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" t="s">
+        <v>14</v>
+      </c>
+      <c r="F38" t="s">
+        <v>24</v>
+      </c>
+      <c r="G38" t="s">
+        <v>24</v>
+      </c>
+      <c r="H38" t="s">
+        <v>24</v>
+      </c>
+      <c r="J38" t="s">
+        <v>24</v>
+      </c>
+      <c r="K38" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>93</v>
+      </c>
+      <c r="C39" t="s">
+        <v>94</v>
+      </c>
+      <c r="D39" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" t="s">
+        <v>14</v>
+      </c>
+      <c r="F39" t="s">
+        <v>289</v>
+      </c>
+      <c r="G39" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" t="s">
+        <v>290</v>
+      </c>
+      <c r="I39" t="s">
+        <v>291</v>
+      </c>
+      <c r="J39" t="s">
+        <v>20</v>
+      </c>
+      <c r="K39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>95</v>
+      </c>
+      <c r="C40" t="s">
+        <v>96</v>
+      </c>
+      <c r="D40" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" t="s">
+        <v>14</v>
+      </c>
+      <c r="F40" t="s">
+        <v>292</v>
+      </c>
+      <c r="G40" t="s">
+        <v>272</v>
+      </c>
+      <c r="H40" t="s">
+        <v>272</v>
+      </c>
+      <c r="J40" t="s">
+        <v>20</v>
+      </c>
+      <c r="K40" t="s">
         <v>263</v>
       </c>
-      <c r="L34" s="10"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B35" t="s">
-        <v>71</v>
-      </c>
-      <c r="C35" t="s">
-        <v>72</v>
-      </c>
-      <c r="D35" t="s">
-        <v>13</v>
-      </c>
-      <c r="E35" t="s">
-        <v>14</v>
-      </c>
-      <c r="F35" t="s">
-        <v>24</v>
-      </c>
-      <c r="G35" t="s">
-        <v>24</v>
-      </c>
-      <c r="H35" t="s">
-        <v>24</v>
-      </c>
-      <c r="J35" t="s">
-        <v>24</v>
-      </c>
-      <c r="K35" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B36" t="s">
-        <v>73</v>
-      </c>
-      <c r="C36" t="s">
-        <v>74</v>
-      </c>
-      <c r="D36" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" t="s">
-        <v>14</v>
-      </c>
-      <c r="F36" t="s">
-        <v>24</v>
-      </c>
-      <c r="G36" t="s">
-        <v>24</v>
-      </c>
-      <c r="H36" t="s">
-        <v>24</v>
-      </c>
-      <c r="J36" t="s">
-        <v>24</v>
-      </c>
-      <c r="K36" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B37" t="s">
-        <v>75</v>
-      </c>
-      <c r="C37" t="s">
-        <v>76</v>
-      </c>
-      <c r="D37" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" t="s">
-        <v>14</v>
-      </c>
-      <c r="F37" t="s">
-        <v>24</v>
-      </c>
-      <c r="G37" t="s">
-        <v>24</v>
-      </c>
-      <c r="H37" t="s">
-        <v>24</v>
-      </c>
-      <c r="J37" t="s">
-        <v>24</v>
-      </c>
-      <c r="K37" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B38" t="s">
-        <v>77</v>
-      </c>
-      <c r="C38" t="s">
-        <v>78</v>
-      </c>
-      <c r="D38" t="s">
-        <v>13</v>
-      </c>
-      <c r="E38" t="s">
-        <v>14</v>
-      </c>
-      <c r="F38" t="s">
-        <v>24</v>
-      </c>
-      <c r="G38" t="s">
-        <v>24</v>
-      </c>
-      <c r="H38" t="s">
-        <v>24</v>
-      </c>
-      <c r="J38" t="s">
-        <v>24</v>
-      </c>
-      <c r="K38" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B39" t="s">
-        <v>79</v>
-      </c>
-      <c r="C39" t="s">
-        <v>80</v>
-      </c>
-      <c r="D39" t="s">
-        <v>13</v>
-      </c>
-      <c r="E39" t="s">
-        <v>14</v>
-      </c>
-      <c r="F39" t="s">
-        <v>24</v>
-      </c>
-      <c r="G39" t="s">
-        <v>24</v>
-      </c>
-      <c r="H39" t="s">
-        <v>24</v>
-      </c>
-      <c r="J39" t="s">
-        <v>24</v>
-      </c>
-      <c r="K39" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B40" t="s">
-        <v>81</v>
-      </c>
-      <c r="C40" t="s">
-        <v>82</v>
-      </c>
-      <c r="D40" t="s">
-        <v>13</v>
-      </c>
-      <c r="E40" t="s">
-        <v>14</v>
-      </c>
-      <c r="F40" t="s">
-        <v>24</v>
-      </c>
-      <c r="G40" t="s">
-        <v>24</v>
-      </c>
-      <c r="H40" t="s">
-        <v>24</v>
-      </c>
-      <c r="J40" t="s">
-        <v>24</v>
-      </c>
-      <c r="K40" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C41" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="D41" t="s">
         <v>13</v>
@@ -2824,28 +2762,28 @@
       <c r="E41" t="s">
         <v>14</v>
       </c>
-      <c r="F41" t="s">
-        <v>24</v>
-      </c>
-      <c r="G41" t="s">
-        <v>24</v>
-      </c>
-      <c r="H41" t="s">
+      <c r="F41" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>24</v>
       </c>
       <c r="J41" t="s">
         <v>24</v>
       </c>
       <c r="K41" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="C42" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="D42" t="s">
         <v>13</v>
@@ -2853,17 +2791,14 @@
       <c r="E42" t="s">
         <v>14</v>
       </c>
-      <c r="F42" t="s">
-        <v>285</v>
-      </c>
-      <c r="G42" t="s">
+      <c r="F42" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="G42" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H42" t="s">
-        <v>284</v>
-      </c>
-      <c r="I42" t="s">
-        <v>286</v>
+      <c r="H42" s="10" t="s">
+        <v>341</v>
       </c>
       <c r="J42" t="s">
         <v>20</v>
@@ -2872,12 +2807,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="C43" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="D43" t="s">
         <v>13</v>
@@ -2885,31 +2820,29 @@
       <c r="E43" t="s">
         <v>14</v>
       </c>
-      <c r="F43" t="s">
-        <v>287</v>
-      </c>
-      <c r="G43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H43" t="s">
-        <v>288</v>
-      </c>
-      <c r="I43" t="s">
-        <v>289</v>
-      </c>
-      <c r="J43" t="s">
+      <c r="F43" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="I43" s="11"/>
+      <c r="J43" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K43" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="K43" s="10" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C44" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="D44" t="s">
         <v>13</v>
@@ -2930,15 +2863,15 @@
         <v>24</v>
       </c>
       <c r="K44" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="C45" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="D45" t="s">
         <v>13</v>
@@ -2959,15 +2892,15 @@
         <v>24</v>
       </c>
       <c r="K45" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="C46" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D46" t="s">
         <v>13</v>
@@ -2976,30 +2909,27 @@
         <v>14</v>
       </c>
       <c r="F46" t="s">
-        <v>290</v>
+        <v>24</v>
       </c>
       <c r="G46" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H46" t="s">
-        <v>291</v>
-      </c>
-      <c r="I46" t="s">
-        <v>292</v>
+        <v>24</v>
       </c>
       <c r="J46" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K46" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C47" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D47" t="s">
         <v>13</v>
@@ -3008,27 +2938,27 @@
         <v>14</v>
       </c>
       <c r="F47" t="s">
-        <v>293</v>
+        <v>24</v>
       </c>
       <c r="G47" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="H47" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="J47" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K47" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="C48" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="D48" t="s">
         <v>13</v>
@@ -3036,28 +2966,28 @@
       <c r="E48" t="s">
         <v>14</v>
       </c>
-      <c r="F48" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="G48" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="H48" s="10" t="s">
+      <c r="F48" t="s">
+        <v>24</v>
+      </c>
+      <c r="G48" t="s">
+        <v>24</v>
+      </c>
+      <c r="H48" t="s">
         <v>24</v>
       </c>
       <c r="J48" t="s">
         <v>24</v>
       </c>
       <c r="K48" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="C49" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="D49" t="s">
         <v>13</v>
@@ -3065,28 +2995,28 @@
       <c r="E49" t="s">
         <v>14</v>
       </c>
-      <c r="F49" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="G49" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>342</v>
+      <c r="F49" t="s">
+        <v>24</v>
+      </c>
+      <c r="G49" t="s">
+        <v>24</v>
+      </c>
+      <c r="H49" t="s">
+        <v>24</v>
       </c>
       <c r="J49" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K49" t="s">
-        <v>21</v>
+        <v>347</v>
       </c>
     </row>
     <row r="50" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="C50" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="D50" t="s">
         <v>13</v>
@@ -3098,10 +3028,10 @@
         <v>294</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I50" s="11"/>
       <c r="J50" s="10" t="s">
@@ -3110,13 +3040,14 @@
       <c r="K50" s="10" t="s">
         <v>263</v>
       </c>
+      <c r="L50" s="10"/>
     </row>
     <row r="51" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="C51" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="D51" t="s">
         <v>13</v>
@@ -3137,15 +3068,15 @@
         <v>24</v>
       </c>
       <c r="K51" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="52" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="C52" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="D52" t="s">
         <v>13</v>
@@ -3166,15 +3097,15 @@
         <v>24</v>
       </c>
       <c r="K52" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="53" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="C53" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="D53" t="s">
         <v>13</v>
@@ -3195,15 +3126,15 @@
         <v>24</v>
       </c>
       <c r="K53" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="54" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="C54" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D54" t="s">
         <v>13</v>
@@ -3224,15 +3155,15 @@
         <v>24</v>
       </c>
       <c r="K54" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="55" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="C55" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="D55" t="s">
         <v>13</v>
@@ -3253,15 +3184,15 @@
         <v>24</v>
       </c>
       <c r="K55" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="56" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="C56" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D56" t="s">
         <v>13</v>
@@ -3282,15 +3213,15 @@
         <v>24</v>
       </c>
       <c r="K56" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="57" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="C57" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D57" t="s">
         <v>13</v>
@@ -3298,59 +3229,60 @@
       <c r="E57" t="s">
         <v>14</v>
       </c>
-      <c r="F57" s="10" t="s">
+      <c r="F57" t="s">
+        <v>24</v>
+      </c>
+      <c r="G57" t="s">
+        <v>24</v>
+      </c>
+      <c r="H57" t="s">
+        <v>24</v>
+      </c>
+      <c r="J57" t="s">
+        <v>24</v>
+      </c>
+      <c r="K57" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="58" spans="2:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>131</v>
+      </c>
+      <c r="C58" t="s">
+        <v>132</v>
+      </c>
+      <c r="D58" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" t="s">
+        <v>14</v>
+      </c>
+      <c r="F58" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="G57" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="I57" s="11"/>
-      <c r="J57" s="10" t="s">
+      <c r="G58" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H58" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="I58" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="J58" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K57" s="10" t="s">
-        <v>263</v>
-      </c>
-      <c r="L57" s="10"/>
-    </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B58" t="s">
-        <v>117</v>
-      </c>
-      <c r="C58" t="s">
-        <v>118</v>
-      </c>
-      <c r="D58" t="s">
-        <v>13</v>
-      </c>
-      <c r="E58" t="s">
-        <v>14</v>
-      </c>
-      <c r="F58" t="s">
-        <v>24</v>
-      </c>
-      <c r="G58" t="s">
-        <v>24</v>
-      </c>
-      <c r="H58" t="s">
-        <v>24</v>
-      </c>
-      <c r="J58" t="s">
-        <v>24</v>
-      </c>
-      <c r="K58" t="s">
-        <v>348</v>
+      <c r="K58" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="59" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="C59" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="D59" t="s">
         <v>13</v>
@@ -3371,15 +3303,15 @@
         <v>24</v>
       </c>
       <c r="K59" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="60" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C60" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="D60" t="s">
         <v>13</v>
@@ -3400,15 +3332,15 @@
         <v>24</v>
       </c>
       <c r="K60" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="61" spans="2:12" ht="30" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="C61" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="D61" t="s">
         <v>13</v>
@@ -3416,28 +3348,31 @@
       <c r="E61" t="s">
         <v>14</v>
       </c>
-      <c r="F61" t="s">
-        <v>24</v>
-      </c>
-      <c r="G61" t="s">
-        <v>24</v>
-      </c>
-      <c r="H61" t="s">
-        <v>24</v>
-      </c>
-      <c r="J61" t="s">
-        <v>24</v>
-      </c>
-      <c r="K61" t="s">
-        <v>348</v>
+      <c r="F61" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="G61" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H61" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="I61" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="J61" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K61" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="62" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="C62" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="D62" t="s">
         <v>13</v>
@@ -3458,15 +3393,15 @@
         <v>24</v>
       </c>
       <c r="K62" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="63" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="C63" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="D63" t="s">
         <v>13</v>
@@ -3487,15 +3422,15 @@
         <v>24</v>
       </c>
       <c r="K63" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="64" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="C64" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="D64" t="s">
         <v>13</v>
@@ -3504,27 +3439,27 @@
         <v>14</v>
       </c>
       <c r="F64" t="s">
-        <v>24</v>
+        <v>301</v>
       </c>
       <c r="G64" t="s">
-        <v>24</v>
+        <v>272</v>
       </c>
       <c r="H64" t="s">
-        <v>24</v>
+        <v>272</v>
       </c>
       <c r="J64" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="K64" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="C65" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="D65" t="s">
         <v>13</v>
@@ -3532,60 +3467,61 @@
       <c r="E65" t="s">
         <v>14</v>
       </c>
-      <c r="F65" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="G65" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="I65" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="J65" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="K65" s="10" t="s">
-        <v>21</v>
+      <c r="F65" t="s">
+        <v>24</v>
+      </c>
+      <c r="G65" t="s">
+        <v>24</v>
+      </c>
+      <c r="H65" t="s">
+        <v>24</v>
+      </c>
+      <c r="J65" t="s">
+        <v>24</v>
+      </c>
+      <c r="K65" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B66" t="s">
-        <v>133</v>
-      </c>
-      <c r="C66" t="s">
-        <v>134</v>
-      </c>
-      <c r="D66" t="s">
-        <v>13</v>
-      </c>
-      <c r="E66" t="s">
-        <v>14</v>
-      </c>
-      <c r="F66" t="s">
-        <v>24</v>
-      </c>
-      <c r="G66" t="s">
-        <v>24</v>
-      </c>
-      <c r="H66" t="s">
-        <v>24</v>
-      </c>
-      <c r="J66" t="s">
-        <v>24</v>
-      </c>
-      <c r="K66" t="s">
-        <v>348</v>
+      <c r="A66" s="13"/>
+      <c r="B66" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F66" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="G66" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="H66" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="I66" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="J66" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="K66" s="10" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="C67" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="D67" t="s">
         <v>13</v>
@@ -3606,15 +3542,15 @@
         <v>24</v>
       </c>
       <c r="K67" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="C68" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="D68" t="s">
         <v>13</v>
@@ -3622,31 +3558,28 @@
       <c r="E68" t="s">
         <v>14</v>
       </c>
-      <c r="F68" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="G68" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H68" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="I68" s="12" t="s">
-        <v>301</v>
-      </c>
-      <c r="J68" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="K68" s="10" t="s">
-        <v>21</v>
+      <c r="F68" t="s">
+        <v>24</v>
+      </c>
+      <c r="G68" t="s">
+        <v>24</v>
+      </c>
+      <c r="H68" t="s">
+        <v>24</v>
+      </c>
+      <c r="J68" t="s">
+        <v>24</v>
+      </c>
+      <c r="K68" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="C69" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="D69" t="s">
         <v>13</v>
@@ -3667,15 +3600,15 @@
         <v>24</v>
       </c>
       <c r="K69" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="C70" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="D70" t="s">
         <v>13</v>
@@ -3696,15 +3629,15 @@
         <v>24</v>
       </c>
       <c r="K70" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="C71" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="D71" t="s">
         <v>13</v>
@@ -3713,27 +3646,27 @@
         <v>14</v>
       </c>
       <c r="F71" t="s">
-        <v>302</v>
+        <v>24</v>
       </c>
       <c r="G71" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="H71" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="J71" t="s">
-        <v>145</v>
+        <v>24</v>
       </c>
       <c r="K71" t="s">
-        <v>263</v>
+        <v>347</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="C72" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="D72" t="s">
         <v>13</v>
@@ -3754,48 +3687,44 @@
         <v>24</v>
       </c>
       <c r="K72" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A73" s="13"/>
-      <c r="B73" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="C73" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="D73" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E73" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F73" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="G73" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="I73" s="15" t="s">
-        <v>344</v>
-      </c>
-      <c r="J73" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="K73" s="10" t="s">
-        <v>17</v>
+      <c r="B73" t="s">
+        <v>162</v>
+      </c>
+      <c r="C73" t="s">
+        <v>163</v>
+      </c>
+      <c r="D73" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73" t="s">
+        <v>14</v>
+      </c>
+      <c r="F73" t="s">
+        <v>24</v>
+      </c>
+      <c r="G73" t="s">
+        <v>24</v>
+      </c>
+      <c r="H73" t="s">
+        <v>24</v>
+      </c>
+      <c r="J73" t="s">
+        <v>24</v>
+      </c>
+      <c r="K73" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="C74" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="D74" t="s">
         <v>13</v>
@@ -3804,27 +3733,30 @@
         <v>14</v>
       </c>
       <c r="F74" t="s">
-        <v>24</v>
+        <v>303</v>
       </c>
       <c r="G74" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H74" t="s">
-        <v>24</v>
+        <v>304</v>
+      </c>
+      <c r="I74" t="s">
+        <v>312</v>
       </c>
       <c r="J74" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K74" t="s">
-        <v>348</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="C75" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="D75" t="s">
         <v>13</v>
@@ -3833,27 +3765,27 @@
         <v>14</v>
       </c>
       <c r="F75" t="s">
-        <v>24</v>
+        <v>305</v>
       </c>
       <c r="G75" t="s">
-        <v>24</v>
+        <v>272</v>
       </c>
       <c r="H75" t="s">
-        <v>24</v>
+        <v>272</v>
       </c>
       <c r="J75" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K75" t="s">
-        <v>348</v>
+        <v>263</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="C76" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="D76" t="s">
         <v>13</v>
@@ -3862,27 +3794,27 @@
         <v>14</v>
       </c>
       <c r="F76" t="s">
-        <v>24</v>
+        <v>306</v>
       </c>
       <c r="G76" t="s">
-        <v>24</v>
-      </c>
-      <c r="H76" t="s">
-        <v>24</v>
+        <v>272</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>272</v>
       </c>
       <c r="J76" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K76" t="s">
-        <v>348</v>
+        <v>263</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="C77" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="D77" t="s">
         <v>13</v>
@@ -3903,15 +3835,15 @@
         <v>24</v>
       </c>
       <c r="K77" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="C78" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="D78" t="s">
         <v>13</v>
@@ -3920,27 +3852,27 @@
         <v>14</v>
       </c>
       <c r="F78" t="s">
-        <v>24</v>
+        <v>307</v>
       </c>
       <c r="G78" t="s">
-        <v>24</v>
+        <v>272</v>
       </c>
       <c r="H78" t="s">
-        <v>24</v>
+        <v>272</v>
       </c>
       <c r="J78" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K78" t="s">
-        <v>348</v>
+        <v>263</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="C79" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="D79" t="s">
         <v>13</v>
@@ -3961,15 +3893,15 @@
         <v>24</v>
       </c>
       <c r="K79" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="C80" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D80" t="s">
         <v>13</v>
@@ -3990,15 +3922,15 @@
         <v>24</v>
       </c>
       <c r="K80" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="81" spans="2:11" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="81" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="C81" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="D81" t="s">
         <v>13</v>
@@ -4007,59 +3939,59 @@
         <v>14</v>
       </c>
       <c r="F81" t="s">
-        <v>304</v>
+        <v>24</v>
       </c>
       <c r="G81" t="s">
+        <v>24</v>
+      </c>
+      <c r="H81" t="s">
+        <v>24</v>
+      </c>
+      <c r="J81" t="s">
+        <v>24</v>
+      </c>
+      <c r="K81" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="82" spans="2:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="B82" t="s">
+        <v>180</v>
+      </c>
+      <c r="C82" t="s">
+        <v>181</v>
+      </c>
+      <c r="D82" t="s">
+        <v>13</v>
+      </c>
+      <c r="E82" t="s">
+        <v>14</v>
+      </c>
+      <c r="F82" t="s">
+        <v>308</v>
+      </c>
+      <c r="G82" t="s">
         <v>15</v>
       </c>
-      <c r="H81" t="s">
-        <v>305</v>
-      </c>
-      <c r="I81" t="s">
+      <c r="H82" t="s">
+        <v>309</v>
+      </c>
+      <c r="I82" s="3" t="s">
         <v>313</v>
-      </c>
-      <c r="J81" t="s">
-        <v>20</v>
-      </c>
-      <c r="K81" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B82" t="s">
-        <v>166</v>
-      </c>
-      <c r="C82" t="s">
-        <v>167</v>
-      </c>
-      <c r="D82" t="s">
-        <v>13</v>
-      </c>
-      <c r="E82" t="s">
-        <v>14</v>
-      </c>
-      <c r="F82" t="s">
-        <v>306</v>
-      </c>
-      <c r="G82" t="s">
-        <v>273</v>
-      </c>
-      <c r="H82" t="s">
-        <v>273</v>
       </c>
       <c r="J82" t="s">
         <v>20</v>
       </c>
       <c r="K82" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="83" spans="2:11" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="83" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="C83" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D83" t="s">
         <v>13</v>
@@ -4068,27 +4000,27 @@
         <v>14</v>
       </c>
       <c r="F83" t="s">
-        <v>307</v>
+        <v>24</v>
       </c>
       <c r="G83" t="s">
-        <v>273</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>273</v>
+        <v>24</v>
+      </c>
+      <c r="H83" t="s">
+        <v>24</v>
       </c>
       <c r="J83" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K83" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="84" spans="2:11" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="84" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="C84" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="D84" t="s">
         <v>13</v>
@@ -4109,15 +4041,15 @@
         <v>24</v>
       </c>
       <c r="K84" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="85" spans="2:11" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="85" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="C85" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="D85" t="s">
         <v>13</v>
@@ -4126,175 +4058,186 @@
         <v>14</v>
       </c>
       <c r="F85" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G85" t="s">
-        <v>273</v>
+        <v>15</v>
       </c>
       <c r="H85" t="s">
-        <v>273</v>
+        <v>311</v>
+      </c>
+      <c r="I85" t="s">
+        <v>314</v>
       </c>
       <c r="J85" t="s">
         <v>20</v>
       </c>
       <c r="K85" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="86" spans="2:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="B86" t="s">
+        <v>188</v>
+      </c>
+      <c r="C86" t="s">
+        <v>189</v>
+      </c>
+      <c r="D86" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" t="s">
+        <v>14</v>
+      </c>
+      <c r="F86" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="G86" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H86" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="I86" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="J86" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K86" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="87" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="B87" t="s">
+        <v>190</v>
+      </c>
+      <c r="C87" t="s">
+        <v>191</v>
+      </c>
+      <c r="D87" t="s">
+        <v>13</v>
+      </c>
+      <c r="E87" t="s">
+        <v>14</v>
+      </c>
+      <c r="F87" t="s">
+        <v>318</v>
+      </c>
+      <c r="G87" t="s">
+        <v>15</v>
+      </c>
+      <c r="H87" t="s">
+        <v>319</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="J87" t="s">
+        <v>20</v>
+      </c>
+      <c r="K87" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="88" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B88" t="s">
+        <v>192</v>
+      </c>
+      <c r="C88" t="s">
+        <v>193</v>
+      </c>
+      <c r="D88" t="s">
+        <v>13</v>
+      </c>
+      <c r="E88" t="s">
+        <v>14</v>
+      </c>
+      <c r="F88" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="G88" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H88" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="I88" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="J88" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K88" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="89" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B89" t="s">
+        <v>194</v>
+      </c>
+      <c r="C89" t="s">
+        <v>195</v>
+      </c>
+      <c r="D89" t="s">
+        <v>13</v>
+      </c>
+      <c r="E89" t="s">
+        <v>14</v>
+      </c>
+      <c r="F89" s="14" t="s">
+        <v>323</v>
+      </c>
+      <c r="G89" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="H89" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="I89" s="12"/>
+      <c r="J89" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K89" s="10" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B86" t="s">
-        <v>174</v>
-      </c>
-      <c r="C86" t="s">
-        <v>175</v>
-      </c>
-      <c r="D86" t="s">
-        <v>13</v>
-      </c>
-      <c r="E86" t="s">
-        <v>14</v>
-      </c>
-      <c r="F86" t="s">
-        <v>24</v>
-      </c>
-      <c r="G86" t="s">
-        <v>24</v>
-      </c>
-      <c r="H86" t="s">
-        <v>24</v>
-      </c>
-      <c r="J86" t="s">
-        <v>24</v>
-      </c>
-      <c r="K86" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="87" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B87" t="s">
-        <v>176</v>
-      </c>
-      <c r="C87" t="s">
-        <v>177</v>
-      </c>
-      <c r="D87" t="s">
-        <v>13</v>
-      </c>
-      <c r="E87" t="s">
-        <v>14</v>
-      </c>
-      <c r="F87" t="s">
-        <v>24</v>
-      </c>
-      <c r="G87" t="s">
-        <v>24</v>
-      </c>
-      <c r="H87" t="s">
-        <v>24</v>
-      </c>
-      <c r="J87" t="s">
-        <v>24</v>
-      </c>
-      <c r="K87" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="88" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B88" t="s">
-        <v>178</v>
-      </c>
-      <c r="C88" t="s">
-        <v>179</v>
-      </c>
-      <c r="D88" t="s">
-        <v>13</v>
-      </c>
-      <c r="E88" t="s">
-        <v>14</v>
-      </c>
-      <c r="F88" t="s">
-        <v>24</v>
-      </c>
-      <c r="G88" t="s">
-        <v>24</v>
-      </c>
-      <c r="H88" t="s">
-        <v>24</v>
-      </c>
-      <c r="J88" t="s">
-        <v>24</v>
-      </c>
-      <c r="K88" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="89" spans="2:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="B89" t="s">
-        <v>180</v>
-      </c>
-      <c r="C89" t="s">
-        <v>181</v>
-      </c>
-      <c r="D89" t="s">
-        <v>13</v>
-      </c>
-      <c r="E89" t="s">
-        <v>14</v>
-      </c>
-      <c r="F89" t="s">
-        <v>309</v>
-      </c>
-      <c r="G89" t="s">
-        <v>15</v>
-      </c>
-      <c r="H89" t="s">
-        <v>310</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="J89" t="s">
+    <row r="90" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B90" t="s">
+        <v>196</v>
+      </c>
+      <c r="C90" t="s">
+        <v>197</v>
+      </c>
+      <c r="D90" t="s">
+        <v>13</v>
+      </c>
+      <c r="E90" t="s">
+        <v>14</v>
+      </c>
+      <c r="F90" s="14" t="s">
+        <v>325</v>
+      </c>
+      <c r="G90" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="H90" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="I90" s="12"/>
+      <c r="J90" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K89" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="90" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B90" t="s">
-        <v>182</v>
-      </c>
-      <c r="C90" t="s">
-        <v>183</v>
-      </c>
-      <c r="D90" t="s">
-        <v>13</v>
-      </c>
-      <c r="E90" t="s">
-        <v>14</v>
-      </c>
-      <c r="F90" t="s">
-        <v>24</v>
-      </c>
-      <c r="G90" t="s">
-        <v>24</v>
-      </c>
-      <c r="H90" t="s">
-        <v>24</v>
-      </c>
-      <c r="J90" t="s">
-        <v>24</v>
-      </c>
-      <c r="K90" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="91" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="K90" s="10" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="91" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="C91" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="D91" t="s">
         <v>13</v>
@@ -4302,28 +4245,30 @@
       <c r="E91" t="s">
         <v>14</v>
       </c>
-      <c r="F91" t="s">
-        <v>24</v>
-      </c>
-      <c r="G91" t="s">
-        <v>24</v>
-      </c>
-      <c r="H91" t="s">
-        <v>24</v>
-      </c>
-      <c r="J91" t="s">
-        <v>24</v>
-      </c>
-      <c r="K91" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="F91" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="G91" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="H91" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="I91" s="12"/>
+      <c r="J91" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K91" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="L91" s="10"/>
+    </row>
+    <row r="92" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="C92" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="D92" t="s">
         <v>13</v>
@@ -4332,62 +4277,57 @@
         <v>14</v>
       </c>
       <c r="F92" t="s">
-        <v>311</v>
+        <v>24</v>
       </c>
       <c r="G92" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H92" t="s">
-        <v>312</v>
-      </c>
-      <c r="I92" t="s">
-        <v>315</v>
+        <v>24</v>
       </c>
       <c r="J92" t="s">
+        <v>24</v>
+      </c>
+      <c r="K92" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="93" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B93" t="s">
+        <v>202</v>
+      </c>
+      <c r="C93" t="s">
+        <v>203</v>
+      </c>
+      <c r="D93" t="s">
+        <v>13</v>
+      </c>
+      <c r="E93" t="s">
+        <v>14</v>
+      </c>
+      <c r="F93" t="s">
+        <v>327</v>
+      </c>
+      <c r="G93" t="s">
+        <v>272</v>
+      </c>
+      <c r="H93" t="s">
+        <v>272</v>
+      </c>
+      <c r="I93" s="3"/>
+      <c r="J93" t="s">
         <v>20</v>
       </c>
-      <c r="K92" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="93" spans="2:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="B93" t="s">
-        <v>188</v>
-      </c>
-      <c r="C93" t="s">
-        <v>189</v>
-      </c>
-      <c r="D93" t="s">
-        <v>13</v>
-      </c>
-      <c r="E93" t="s">
-        <v>14</v>
-      </c>
-      <c r="F93" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="G93" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="I93" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="J93" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="K93" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="94" spans="2:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="K93" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="94" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="C94" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="D94" t="s">
         <v>13</v>
@@ -4396,16 +4336,13 @@
         <v>14</v>
       </c>
       <c r="F94" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="G94" t="s">
         <v>15</v>
       </c>
       <c r="H94" t="s">
-        <v>320</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="J94" t="s">
         <v>20</v>
@@ -4414,12 +4351,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="95" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="C95" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="D95" t="s">
         <v>13</v>
@@ -4427,31 +4364,28 @@
       <c r="E95" t="s">
         <v>14</v>
       </c>
-      <c r="F95" s="10" t="s">
-        <v>322</v>
-      </c>
-      <c r="G95" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="I95" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="J95" s="10" t="s">
+      <c r="F95" t="s">
+        <v>330</v>
+      </c>
+      <c r="G95" t="s">
+        <v>272</v>
+      </c>
+      <c r="H95" t="s">
+        <v>272</v>
+      </c>
+      <c r="J95" t="s">
         <v>20</v>
       </c>
-      <c r="K95" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="96" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="K95" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="96" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="C96" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="D96" t="s">
         <v>13</v>
@@ -4459,90 +4393,86 @@
       <c r="E96" t="s">
         <v>14</v>
       </c>
-      <c r="F96" s="14" t="s">
-        <v>324</v>
-      </c>
-      <c r="G96" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="H96" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="I96" s="12"/>
-      <c r="J96" s="10" t="s">
+      <c r="F96" t="s">
+        <v>24</v>
+      </c>
+      <c r="G96" t="s">
+        <v>24</v>
+      </c>
+      <c r="H96" t="s">
+        <v>24</v>
+      </c>
+      <c r="J96" t="s">
+        <v>24</v>
+      </c>
+      <c r="K96" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="97" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B97" t="s">
+        <v>210</v>
+      </c>
+      <c r="C97" t="s">
+        <v>211</v>
+      </c>
+      <c r="D97" t="s">
+        <v>13</v>
+      </c>
+      <c r="E97" t="s">
+        <v>14</v>
+      </c>
+      <c r="F97" t="s">
+        <v>331</v>
+      </c>
+      <c r="G97" t="s">
+        <v>272</v>
+      </c>
+      <c r="H97" t="s">
+        <v>272</v>
+      </c>
+      <c r="J97" t="s">
         <v>20</v>
       </c>
-      <c r="K96" s="10" t="s">
+      <c r="K97" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="97" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B97" t="s">
-        <v>196</v>
-      </c>
-      <c r="C97" t="s">
-        <v>197</v>
-      </c>
-      <c r="D97" t="s">
-        <v>13</v>
-      </c>
-      <c r="E97" t="s">
-        <v>14</v>
-      </c>
-      <c r="F97" s="14" t="s">
-        <v>326</v>
-      </c>
-      <c r="G97" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="H97" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="I97" s="12"/>
-      <c r="J97" s="10" t="s">
+    <row r="98" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B98" t="s">
+        <v>212</v>
+      </c>
+      <c r="C98" t="s">
+        <v>213</v>
+      </c>
+      <c r="D98" t="s">
+        <v>13</v>
+      </c>
+      <c r="E98" t="s">
+        <v>14</v>
+      </c>
+      <c r="F98" t="s">
+        <v>332</v>
+      </c>
+      <c r="G98" t="s">
+        <v>272</v>
+      </c>
+      <c r="H98" t="s">
+        <v>272</v>
+      </c>
+      <c r="J98" t="s">
         <v>20</v>
       </c>
-      <c r="K97" s="10" t="s">
+      <c r="K98" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="98" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B98" t="s">
-        <v>198</v>
-      </c>
-      <c r="C98" t="s">
-        <v>199</v>
-      </c>
-      <c r="D98" t="s">
-        <v>13</v>
-      </c>
-      <c r="E98" t="s">
-        <v>14</v>
-      </c>
-      <c r="F98" s="10" t="s">
-        <v>327</v>
-      </c>
-      <c r="G98" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="H98" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="I98" s="12"/>
-      <c r="J98" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="K98" s="10" t="s">
-        <v>263</v>
-      </c>
-      <c r="L98" s="10"/>
-    </row>
-    <row r="99" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="C99" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="D99" t="s">
         <v>13</v>
@@ -4563,15 +4493,15 @@
         <v>24</v>
       </c>
       <c r="K99" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="100" spans="2:12" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="100" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="C100" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="D100" t="s">
         <v>13</v>
@@ -4580,28 +4510,27 @@
         <v>14</v>
       </c>
       <c r="F100" t="s">
-        <v>328</v>
+        <v>24</v>
       </c>
       <c r="G100" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="H100" t="s">
-        <v>273</v>
-      </c>
-      <c r="I100" s="3"/>
+        <v>24</v>
+      </c>
       <c r="J100" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K100" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="101" spans="2:12" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="101" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="C101" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="D101" t="s">
         <v>13</v>
@@ -4610,27 +4539,27 @@
         <v>14</v>
       </c>
       <c r="F101" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="G101" t="s">
-        <v>15</v>
+        <v>272</v>
       </c>
       <c r="H101" t="s">
-        <v>330</v>
+        <v>272</v>
       </c>
       <c r="J101" t="s">
         <v>20</v>
       </c>
       <c r="K101" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="102" spans="2:12" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="102" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="C102" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="D102" t="s">
         <v>13</v>
@@ -4639,27 +4568,27 @@
         <v>14</v>
       </c>
       <c r="F102" t="s">
-        <v>331</v>
+        <v>24</v>
       </c>
       <c r="G102" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="H102" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="J102" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K102" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="103" spans="2:12" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="103" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="C103" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="D103" t="s">
         <v>13</v>
@@ -4680,15 +4609,15 @@
         <v>24</v>
       </c>
       <c r="K103" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="104" spans="2:12" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="104" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="C104" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="D104" t="s">
         <v>13</v>
@@ -4697,27 +4626,27 @@
         <v>14</v>
       </c>
       <c r="F104" t="s">
-        <v>332</v>
+        <v>24</v>
       </c>
       <c r="G104" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="H104" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="J104" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K104" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="105" spans="2:12" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="105" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="C105" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="D105" t="s">
         <v>13</v>
@@ -4726,27 +4655,27 @@
         <v>14</v>
       </c>
       <c r="F105" t="s">
-        <v>333</v>
+        <v>24</v>
       </c>
       <c r="G105" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="H105" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="J105" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K105" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="106" spans="2:12" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="106" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="C106" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="D106" t="s">
         <v>13</v>
@@ -4767,15 +4696,15 @@
         <v>24</v>
       </c>
       <c r="K106" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="107" spans="2:12" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="107" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="C107" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="D107" t="s">
         <v>13</v>
@@ -4796,15 +4725,15 @@
         <v>24</v>
       </c>
       <c r="K107" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="108" spans="2:12" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="108" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="C108" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D108" t="s">
         <v>13</v>
@@ -4813,27 +4742,27 @@
         <v>14</v>
       </c>
       <c r="F108" t="s">
-        <v>334</v>
+        <v>24</v>
       </c>
       <c r="G108" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="H108" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="J108" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K108" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="109" spans="2:12" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="109" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="C109" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="D109" t="s">
         <v>13</v>
@@ -4854,15 +4783,15 @@
         <v>24</v>
       </c>
       <c r="K109" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="110" spans="2:12" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="110" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C110" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="D110" t="s">
         <v>13</v>
@@ -4883,15 +4812,15 @@
         <v>24</v>
       </c>
       <c r="K110" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="111" spans="2:12" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="111" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="C111" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="D111" t="s">
         <v>13</v>
@@ -4912,15 +4841,15 @@
         <v>24</v>
       </c>
       <c r="K111" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="112" spans="2:12" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="C112" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="D112" t="s">
         <v>13</v>
@@ -4941,15 +4870,15 @@
         <v>24</v>
       </c>
       <c r="K112" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="113" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="C113" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D113" t="s">
         <v>13</v>
@@ -4970,15 +4899,15 @@
         <v>24</v>
       </c>
       <c r="K113" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="114" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="C114" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="D114" t="s">
         <v>13</v>
@@ -4999,15 +4928,15 @@
         <v>24</v>
       </c>
       <c r="K114" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="115" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="C115" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="D115" t="s">
         <v>13</v>
@@ -5028,15 +4957,15 @@
         <v>24</v>
       </c>
       <c r="K115" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="116" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="C116" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="D116" t="s">
         <v>13</v>
@@ -5057,15 +4986,15 @@
         <v>24</v>
       </c>
       <c r="K116" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="117" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="C117" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D117" t="s">
         <v>13</v>
@@ -5086,15 +5015,15 @@
         <v>24</v>
       </c>
       <c r="K117" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="118" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="C118" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D118" t="s">
         <v>13</v>
@@ -5115,15 +5044,15 @@
         <v>24</v>
       </c>
       <c r="K118" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="119" spans="2:11" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="119" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="C119" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D119" t="s">
         <v>13</v>
@@ -5132,27 +5061,30 @@
         <v>14</v>
       </c>
       <c r="F119" t="s">
-        <v>24</v>
+        <v>334</v>
       </c>
       <c r="G119" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H119" t="s">
-        <v>24</v>
+        <v>335</v>
+      </c>
+      <c r="I119" s="3" t="s">
+        <v>336</v>
       </c>
       <c r="J119" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K119" t="s">
-        <v>348</v>
+        <v>21</v>
       </c>
     </row>
     <row r="120" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="C120" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D120" t="s">
         <v>13</v>
@@ -5173,244 +5105,38 @@
         <v>24</v>
       </c>
       <c r="K120" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="121" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="C121" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="D121" t="s">
-        <v>13</v>
+        <v>260</v>
       </c>
       <c r="E121" t="s">
         <v>14</v>
       </c>
-      <c r="F121" t="s">
-        <v>24</v>
-      </c>
-      <c r="G121" t="s">
-        <v>24</v>
-      </c>
-      <c r="H121" t="s">
-        <v>24</v>
-      </c>
-      <c r="J121" t="s">
-        <v>24</v>
-      </c>
-      <c r="K121" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="122" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B122" t="s">
-        <v>246</v>
-      </c>
-      <c r="C122" t="s">
-        <v>247</v>
-      </c>
-      <c r="D122" t="s">
-        <v>13</v>
-      </c>
-      <c r="E122" t="s">
-        <v>14</v>
-      </c>
-      <c r="F122" t="s">
-        <v>24</v>
-      </c>
-      <c r="G122" t="s">
-        <v>24</v>
-      </c>
-      <c r="H122" t="s">
-        <v>24</v>
-      </c>
-      <c r="J122" t="s">
-        <v>24</v>
-      </c>
-      <c r="K122" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="123" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B123" t="s">
-        <v>248</v>
-      </c>
-      <c r="C123" t="s">
-        <v>249</v>
-      </c>
-      <c r="D123" t="s">
-        <v>13</v>
-      </c>
-      <c r="E123" t="s">
-        <v>14</v>
-      </c>
-      <c r="F123" t="s">
-        <v>24</v>
-      </c>
-      <c r="G123" t="s">
-        <v>24</v>
-      </c>
-      <c r="H123" t="s">
-        <v>24</v>
-      </c>
-      <c r="J123" t="s">
-        <v>24</v>
-      </c>
-      <c r="K123" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="124" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B124" t="s">
-        <v>250</v>
-      </c>
-      <c r="C124" t="s">
-        <v>251</v>
-      </c>
-      <c r="D124" t="s">
-        <v>13</v>
-      </c>
-      <c r="E124" t="s">
-        <v>14</v>
-      </c>
-      <c r="F124" t="s">
-        <v>24</v>
-      </c>
-      <c r="G124" t="s">
-        <v>24</v>
-      </c>
-      <c r="H124" t="s">
-        <v>24</v>
-      </c>
-      <c r="J124" t="s">
-        <v>24</v>
-      </c>
-      <c r="K124" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="125" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B125" t="s">
-        <v>252</v>
-      </c>
-      <c r="C125" t="s">
-        <v>253</v>
-      </c>
-      <c r="D125" t="s">
-        <v>13</v>
-      </c>
-      <c r="E125" t="s">
-        <v>14</v>
-      </c>
-      <c r="F125" t="s">
-        <v>24</v>
-      </c>
-      <c r="G125" t="s">
-        <v>24</v>
-      </c>
-      <c r="H125" t="s">
-        <v>24</v>
-      </c>
-      <c r="J125" t="s">
-        <v>24</v>
-      </c>
-      <c r="K125" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="126" spans="2:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="B126" t="s">
-        <v>254</v>
-      </c>
-      <c r="C126" t="s">
-        <v>255</v>
-      </c>
-      <c r="D126" t="s">
-        <v>13</v>
-      </c>
-      <c r="E126" t="s">
-        <v>14</v>
-      </c>
-      <c r="F126" t="s">
-        <v>335</v>
-      </c>
-      <c r="G126" t="s">
-        <v>15</v>
-      </c>
-      <c r="H126" t="s">
-        <v>336</v>
-      </c>
-      <c r="I126" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="J126" t="s">
+      <c r="F121" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="G121" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="H121" s="6">
+        <v>1</v>
+      </c>
+      <c r="I121" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="J121" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="K126" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B127" t="s">
-        <v>256</v>
-      </c>
-      <c r="C127" t="s">
-        <v>257</v>
-      </c>
-      <c r="D127" t="s">
-        <v>13</v>
-      </c>
-      <c r="E127" t="s">
-        <v>14</v>
-      </c>
-      <c r="F127" t="s">
-        <v>24</v>
-      </c>
-      <c r="G127" t="s">
-        <v>24</v>
-      </c>
-      <c r="H127" t="s">
-        <v>24</v>
-      </c>
-      <c r="J127" t="s">
-        <v>24</v>
-      </c>
-      <c r="K127" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="128" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B128" t="s">
-        <v>258</v>
-      </c>
-      <c r="C128" t="s">
-        <v>259</v>
-      </c>
-      <c r="D128" t="s">
-        <v>260</v>
-      </c>
-      <c r="E128" t="s">
-        <v>14</v>
-      </c>
-      <c r="F128" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="G128" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="H128" s="6">
-        <v>1</v>
-      </c>
-      <c r="I128" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="J128" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K128" s="8" t="s">
+      <c r="K121" s="8" t="s">
         <v>263</v>
       </c>
     </row>
@@ -5421,27 +5147,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Zeit xmlns="b63cdcf7-47fa-43f6-87e5-23b415b5c413" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b63cdcf7-47fa-43f6-87e5-23b415b5c413">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="12535b08-222e-45d2-b6db-15019f1afee6" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100B1DC67C611DD5E4D81775F9F3E26A7B2" ma:contentTypeVersion="16" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="7f379a5812b480a74f9d031be5f88a83">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b63cdcf7-47fa-43f6-87e5-23b415b5c413" xmlns:ns3="12535b08-222e-45d2-b6db-15019f1afee6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dbce1e37d7de67e1c835013ca0ee7a7c" ns2:_="" ns3:_="">
     <xsd:import namespace="b63cdcf7-47fa-43f6-87e5-23b415b5c413"/>
@@ -5682,32 +5387,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7C1076D-2C61-4BAC-A503-5A4B20CD35B7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="b63cdcf7-47fa-43f6-87e5-23b415b5c413"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="12535b08-222e-45d2-b6db-15019f1afee6"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70A53FE4-D237-4764-9B07-7D2AFF4EC446}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Zeit xmlns="b63cdcf7-47fa-43f6-87e5-23b415b5c413" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b63cdcf7-47fa-43f6-87e5-23b415b5c413">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="12535b08-222e-45d2-b6db-15019f1afee6" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EDAC40C-4E49-457D-B6B8-71BBCE94E8A2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5724,4 +5425,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70A53FE4-D237-4764-9B07-7D2AFF4EC446}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7C1076D-2C61-4BAC-A503-5A4B20CD35B7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="b63cdcf7-47fa-43f6-87e5-23b415b5c413"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="12535b08-222e-45d2-b6db-15019f1afee6"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/analyst/Franzi/rmonize/data_proc_elem/DPE_DEGS1_FRANZI.xlsx
+++ b/analyst/Franzi/rmonize/data_proc_elem/DPE_DEGS1_FRANZI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Franzi\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0A7CDC-9D01-4312-AF99-AC3E020E9DF0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA45841C-FD88-402D-8173-02024E4B6928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -978,9 +978,6 @@
     <t>mfsaft;mgsaft</t>
   </si>
   <si>
-    <t>mfast + mgsaft</t>
-  </si>
-  <si>
     <t>Summe aus Fruchtsaft + Gemüsesaft</t>
   </si>
   <si>
@@ -1076,6 +1073,9 @@
   </si>
   <si>
     <t>mrgem;mggem</t>
+  </si>
+  <si>
+    <t>mfsaft + mgsaft</t>
   </si>
 </sst>
 </file>
@@ -1210,9 +1210,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1250,9 +1250,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1285,26 +1285,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1337,26 +1320,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1603,7 +1569,7 @@
         <v>266</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="J2" t="s">
         <v>16</v>
@@ -1670,7 +1636,7 @@
         <v>24</v>
       </c>
       <c r="K4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -1687,7 +1653,7 @@
         <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G5" t="s">
         <v>15</v>
@@ -1731,7 +1697,7 @@
         <v>24</v>
       </c>
       <c r="K6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -1760,7 +1726,7 @@
         <v>24</v>
       </c>
       <c r="K7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -1789,7 +1755,7 @@
         <v>24</v>
       </c>
       <c r="K8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -1818,7 +1784,7 @@
         <v>24</v>
       </c>
       <c r="K9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1847,7 +1813,7 @@
         <v>24</v>
       </c>
       <c r="K10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1876,7 +1842,7 @@
         <v>24</v>
       </c>
       <c r="K11" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1905,7 +1871,7 @@
         <v>24</v>
       </c>
       <c r="K12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1934,7 +1900,7 @@
         <v>24</v>
       </c>
       <c r="K13" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1963,7 +1929,7 @@
         <v>24</v>
       </c>
       <c r="K14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -2024,7 +1990,7 @@
         <v>24</v>
       </c>
       <c r="K16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="17" spans="2:12" ht="30" x14ac:dyDescent="0.25">
@@ -2173,7 +2139,7 @@
         <v>24</v>
       </c>
       <c r="K21" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.25">
@@ -2190,16 +2156,16 @@
         <v>14</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G22" s="10" t="s">
         <v>15</v>
       </c>
       <c r="H22" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="I22" t="s">
         <v>338</v>
-      </c>
-      <c r="I22" t="s">
-        <v>339</v>
       </c>
       <c r="J22" t="s">
         <v>20</v>
@@ -2263,7 +2229,7 @@
         <v>24</v>
       </c>
       <c r="K24" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="25" spans="2:12" ht="60" x14ac:dyDescent="0.25">
@@ -2289,7 +2255,7 @@
         <v>272</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="J25" s="10" t="s">
         <v>16</v>
@@ -2313,7 +2279,7 @@
         <v>14</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>272</v>
@@ -2322,7 +2288,7 @@
         <v>272</v>
       </c>
       <c r="I26" s="16" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="J26" s="10" t="s">
         <v>16</v>
@@ -2389,7 +2355,7 @@
         <v>24</v>
       </c>
       <c r="K28" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.25">
@@ -2418,7 +2384,7 @@
         <v>24</v>
       </c>
       <c r="K29" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.25">
@@ -2447,7 +2413,7 @@
         <v>24</v>
       </c>
       <c r="K30" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.25">
@@ -2476,7 +2442,7 @@
         <v>24</v>
       </c>
       <c r="K31" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.25">
@@ -2505,7 +2471,7 @@
         <v>24</v>
       </c>
       <c r="K32" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
@@ -2534,7 +2500,7 @@
         <v>24</v>
       </c>
       <c r="K33" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
@@ -2563,7 +2529,7 @@
         <v>24</v>
       </c>
       <c r="K34" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
@@ -2656,7 +2622,7 @@
         <v>24</v>
       </c>
       <c r="K37" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
@@ -2685,7 +2651,7 @@
         <v>24</v>
       </c>
       <c r="K38" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
@@ -2775,7 +2741,7 @@
         <v>24</v>
       </c>
       <c r="K41" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
@@ -2792,13 +2758,13 @@
         <v>14</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G42" s="10" t="s">
         <v>15</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J42" t="s">
         <v>20</v>
@@ -2863,7 +2829,7 @@
         <v>24</v>
       </c>
       <c r="K44" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
@@ -2892,7 +2858,7 @@
         <v>24</v>
       </c>
       <c r="K45" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
@@ -2921,7 +2887,7 @@
         <v>24</v>
       </c>
       <c r="K46" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
@@ -2950,7 +2916,7 @@
         <v>24</v>
       </c>
       <c r="K47" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
@@ -2979,7 +2945,7 @@
         <v>24</v>
       </c>
       <c r="K48" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.25">
@@ -3008,7 +2974,7 @@
         <v>24</v>
       </c>
       <c r="K49" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="50" spans="2:12" x14ac:dyDescent="0.25">
@@ -3068,7 +3034,7 @@
         <v>24</v>
       </c>
       <c r="K51" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="52" spans="2:12" x14ac:dyDescent="0.25">
@@ -3097,7 +3063,7 @@
         <v>24</v>
       </c>
       <c r="K52" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="53" spans="2:12" x14ac:dyDescent="0.25">
@@ -3126,7 +3092,7 @@
         <v>24</v>
       </c>
       <c r="K53" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="54" spans="2:12" x14ac:dyDescent="0.25">
@@ -3155,7 +3121,7 @@
         <v>24</v>
       </c>
       <c r="K54" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="55" spans="2:12" x14ac:dyDescent="0.25">
@@ -3184,7 +3150,7 @@
         <v>24</v>
       </c>
       <c r="K55" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="56" spans="2:12" x14ac:dyDescent="0.25">
@@ -3213,7 +3179,7 @@
         <v>24</v>
       </c>
       <c r="K56" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="57" spans="2:12" x14ac:dyDescent="0.25">
@@ -3242,7 +3208,7 @@
         <v>24</v>
       </c>
       <c r="K57" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="58" spans="2:12" ht="45" x14ac:dyDescent="0.25">
@@ -3303,7 +3269,7 @@
         <v>24</v>
       </c>
       <c r="K59" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="60" spans="2:12" x14ac:dyDescent="0.25">
@@ -3332,7 +3298,7 @@
         <v>24</v>
       </c>
       <c r="K60" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="61" spans="2:12" ht="30" x14ac:dyDescent="0.25">
@@ -3393,7 +3359,7 @@
         <v>24</v>
       </c>
       <c r="K62" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="63" spans="2:12" x14ac:dyDescent="0.25">
@@ -3422,7 +3388,7 @@
         <v>24</v>
       </c>
       <c r="K63" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="64" spans="2:12" x14ac:dyDescent="0.25">
@@ -3480,7 +3446,7 @@
         <v>24</v>
       </c>
       <c r="K65" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -3507,7 +3473,7 @@
         <v>272</v>
       </c>
       <c r="I66" s="15" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J66" s="10" t="s">
         <v>282</v>
@@ -3542,7 +3508,7 @@
         <v>24</v>
       </c>
       <c r="K67" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -3571,7 +3537,7 @@
         <v>24</v>
       </c>
       <c r="K68" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -3600,7 +3566,7 @@
         <v>24</v>
       </c>
       <c r="K69" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -3629,7 +3595,7 @@
         <v>24</v>
       </c>
       <c r="K70" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -3658,7 +3624,7 @@
         <v>24</v>
       </c>
       <c r="K71" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -3687,7 +3653,7 @@
         <v>24</v>
       </c>
       <c r="K72" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -3716,7 +3682,7 @@
         <v>24</v>
       </c>
       <c r="K73" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -3835,7 +3801,7 @@
         <v>24</v>
       </c>
       <c r="K77" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -3893,7 +3859,7 @@
         <v>24</v>
       </c>
       <c r="K79" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -3922,7 +3888,7 @@
         <v>24</v>
       </c>
       <c r="K80" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="2:12" x14ac:dyDescent="0.25">
@@ -3951,7 +3917,7 @@
         <v>24</v>
       </c>
       <c r="K81" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="2:12" ht="45" x14ac:dyDescent="0.25">
@@ -4012,7 +3978,7 @@
         <v>24</v>
       </c>
       <c r="K83" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="2:12" x14ac:dyDescent="0.25">
@@ -4041,7 +4007,7 @@
         <v>24</v>
       </c>
       <c r="K84" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="85" spans="2:12" x14ac:dyDescent="0.25">
@@ -4096,10 +4062,10 @@
         <v>15</v>
       </c>
       <c r="H86" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="I86" s="12" t="s">
         <v>316</v>
-      </c>
-      <c r="I86" s="12" t="s">
-        <v>317</v>
       </c>
       <c r="J86" s="10" t="s">
         <v>20</v>
@@ -4122,16 +4088,16 @@
         <v>14</v>
       </c>
       <c r="F87" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G87" t="s">
         <v>15</v>
       </c>
       <c r="H87" t="s">
+        <v>318</v>
+      </c>
+      <c r="I87" s="3" t="s">
         <v>319</v>
-      </c>
-      <c r="I87" s="3" t="s">
-        <v>320</v>
       </c>
       <c r="J87" t="s">
         <v>20</v>
@@ -4154,16 +4120,16 @@
         <v>14</v>
       </c>
       <c r="F88" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G88" s="10" t="s">
         <v>15</v>
       </c>
       <c r="H88" s="10" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I88" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J88" s="10" t="s">
         <v>20</v>
@@ -4186,7 +4152,7 @@
         <v>14</v>
       </c>
       <c r="F89" s="14" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G89" s="10" t="s">
         <v>272</v>
@@ -4216,7 +4182,7 @@
         <v>14</v>
       </c>
       <c r="F90" s="14" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G90" s="10" t="s">
         <v>272</v>
@@ -4246,7 +4212,7 @@
         <v>14</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G91" s="10" t="s">
         <v>272</v>
@@ -4289,7 +4255,7 @@
         <v>24</v>
       </c>
       <c r="K92" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="93" spans="2:12" x14ac:dyDescent="0.25">
@@ -4306,7 +4272,7 @@
         <v>14</v>
       </c>
       <c r="F93" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G93" t="s">
         <v>272</v>
@@ -4336,13 +4302,13 @@
         <v>14</v>
       </c>
       <c r="F94" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G94" t="s">
         <v>15</v>
       </c>
       <c r="H94" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J94" t="s">
         <v>20</v>
@@ -4365,7 +4331,7 @@
         <v>14</v>
       </c>
       <c r="F95" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G95" t="s">
         <v>272</v>
@@ -4406,7 +4372,7 @@
         <v>24</v>
       </c>
       <c r="K96" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="97" spans="2:11" x14ac:dyDescent="0.25">
@@ -4423,7 +4389,7 @@
         <v>14</v>
       </c>
       <c r="F97" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G97" t="s">
         <v>272</v>
@@ -4452,7 +4418,7 @@
         <v>14</v>
       </c>
       <c r="F98" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G98" t="s">
         <v>272</v>
@@ -4493,7 +4459,7 @@
         <v>24</v>
       </c>
       <c r="K99" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="100" spans="2:11" x14ac:dyDescent="0.25">
@@ -4522,7 +4488,7 @@
         <v>24</v>
       </c>
       <c r="K100" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="101" spans="2:11" x14ac:dyDescent="0.25">
@@ -4539,7 +4505,7 @@
         <v>14</v>
       </c>
       <c r="F101" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G101" t="s">
         <v>272</v>
@@ -4580,7 +4546,7 @@
         <v>24</v>
       </c>
       <c r="K102" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="103" spans="2:11" x14ac:dyDescent="0.25">
@@ -4609,7 +4575,7 @@
         <v>24</v>
       </c>
       <c r="K103" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="104" spans="2:11" x14ac:dyDescent="0.25">
@@ -4638,7 +4604,7 @@
         <v>24</v>
       </c>
       <c r="K104" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="105" spans="2:11" x14ac:dyDescent="0.25">
@@ -4667,7 +4633,7 @@
         <v>24</v>
       </c>
       <c r="K105" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="106" spans="2:11" x14ac:dyDescent="0.25">
@@ -4696,7 +4662,7 @@
         <v>24</v>
       </c>
       <c r="K106" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="107" spans="2:11" x14ac:dyDescent="0.25">
@@ -4725,7 +4691,7 @@
         <v>24</v>
       </c>
       <c r="K107" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="108" spans="2:11" x14ac:dyDescent="0.25">
@@ -4754,7 +4720,7 @@
         <v>24</v>
       </c>
       <c r="K108" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="109" spans="2:11" x14ac:dyDescent="0.25">
@@ -4783,7 +4749,7 @@
         <v>24</v>
       </c>
       <c r="K109" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="110" spans="2:11" x14ac:dyDescent="0.25">
@@ -4812,7 +4778,7 @@
         <v>24</v>
       </c>
       <c r="K110" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="111" spans="2:11" x14ac:dyDescent="0.25">
@@ -4841,7 +4807,7 @@
         <v>24</v>
       </c>
       <c r="K111" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="112" spans="2:11" x14ac:dyDescent="0.25">
@@ -4870,7 +4836,7 @@
         <v>24</v>
       </c>
       <c r="K112" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="113" spans="2:11" x14ac:dyDescent="0.25">
@@ -4899,7 +4865,7 @@
         <v>24</v>
       </c>
       <c r="K113" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="114" spans="2:11" x14ac:dyDescent="0.25">
@@ -4928,7 +4894,7 @@
         <v>24</v>
       </c>
       <c r="K114" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="115" spans="2:11" x14ac:dyDescent="0.25">
@@ -4957,7 +4923,7 @@
         <v>24</v>
       </c>
       <c r="K115" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="116" spans="2:11" x14ac:dyDescent="0.25">
@@ -4986,7 +4952,7 @@
         <v>24</v>
       </c>
       <c r="K116" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="117" spans="2:11" x14ac:dyDescent="0.25">
@@ -5015,7 +4981,7 @@
         <v>24</v>
       </c>
       <c r="K117" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="118" spans="2:11" x14ac:dyDescent="0.25">
@@ -5044,7 +5010,7 @@
         <v>24</v>
       </c>
       <c r="K118" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="119" spans="2:11" ht="30" x14ac:dyDescent="0.25">
@@ -5061,16 +5027,16 @@
         <v>14</v>
       </c>
       <c r="F119" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G119" t="s">
         <v>15</v>
       </c>
       <c r="H119" t="s">
+        <v>334</v>
+      </c>
+      <c r="I119" s="3" t="s">
         <v>335</v>
-      </c>
-      <c r="I119" s="3" t="s">
-        <v>336</v>
       </c>
       <c r="J119" t="s">
         <v>20</v>
@@ -5105,7 +5071,7 @@
         <v>24</v>
       </c>
       <c r="K120" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="121" spans="2:11" x14ac:dyDescent="0.25">
@@ -5147,6 +5113,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100B1DC67C611DD5E4D81775F9F3E26A7B2" ma:contentTypeVersion="16" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="7f379a5812b480a74f9d031be5f88a83">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b63cdcf7-47fa-43f6-87e5-23b415b5c413" xmlns:ns3="12535b08-222e-45d2-b6db-15019f1afee6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dbce1e37d7de67e1c835013ca0ee7a7c" ns2:_="" ns3:_="">
     <xsd:import namespace="b63cdcf7-47fa-43f6-87e5-23b415b5c413"/>
@@ -5387,15 +5362,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5409,6 +5375,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70A53FE4-D237-4764-9B07-7D2AFF4EC446}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EDAC40C-4E49-457D-B6B8-71BBCE94E8A2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5423,14 +5397,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70A53FE4-D237-4764-9B07-7D2AFF4EC446}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
